--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -14,7 +14,7 @@
     <sheet name="历史记录" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -302,7 +302,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR1.1 内容刷新率 (上屏)</a:t>
+              <a:t>KR1.1 内容刷新率 (假转, 管线能力)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -544,7 +544,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR5.1 几何 LUT 复现正确 (1=逐字节复现)</a:t>
+              <a:t>KR4.1 色深</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -586,12 +586,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$158:$A$159</f>
+              <f>'指标趋势'!$A$158:$A$162</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$158:$B$159</f>
+              <f>'指标趋势'!$B$158:$B$162</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -599,6 +599,49 @@
         <ser>
           <idx val="1"/>
           <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!C157</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="triangle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$158:$A$162</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$C$158:$C$162</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!E157</f>
@@ -633,8 +676,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G157</f>
@@ -669,8 +712,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I157</f>
@@ -712,7 +755,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46308"/>
-          <min val="46238"/>
+          <min val="46231"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -754,7 +797,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>是/否</a:t>
+                  <a:t>bit/通道</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -786,7 +829,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR5.2 左右镜像已核实 (1=已核)</a:t>
+              <a:t>KR5.1 几何 LUT 复现正确 (1=逐字节复现)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -828,12 +871,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$175</f>
+              <f>'指标趋势'!$A$175:$A$176</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$175</f>
+              <f>'指标趋势'!$B$175:$B$176</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -953,8 +996,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46238"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1028,7 +1071,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR6.1 停转自动低亮 (1=有)</a:t>
+              <a:t>KR5.2 左右镜像已核实 (1=已核)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1195,8 +1238,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
-          <min val="46306"/>
+          <max val="46309"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1270,7 +1313,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR7.1 丢帧/迟到率</a:t>
+              <a:t>KR6.1 停转自动低亮 (1=有)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1327,49 +1370,6 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!C208</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="triangle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="ED7D31"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$A$209</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$C$209</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
               <f>'指标趋势'!E208</f>
             </strRef>
           </tx>
@@ -1402,8 +1402,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G208</f>
@@ -1438,8 +1438,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I208</f>
@@ -1480,8 +1480,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1523,7 +1523,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>%</a:t>
+                  <a:t>是/否</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1555,7 +1555,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR7.2 连续无故障运行时长</a:t>
+              <a:t>KR7.1 丢帧/迟到率</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1597,12 +1597,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$226:$A$227</f>
+              <f>'指标趋势'!$A$226</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$226:$B$227</f>
+              <f>'指标趋势'!$B$226</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -1640,12 +1640,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$226:$A$227</f>
+              <f>'指标趋势'!$A$226</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$226:$C$227</f>
+              <f>'指标趋势'!$C$226</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -1765,7 +1765,7 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
+          <max val="46309"/>
           <min val="46307"/>
         </scaling>
         <delete val="0"/>
@@ -1808,7 +1808,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>h</a:t>
+                  <a:t>%</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1840,7 +1840,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.1 上电到出图</a:t>
+              <a:t>KR7.2 连续无故障运行时长</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1882,12 +1882,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$243</f>
+              <f>'指标趋势'!$A$243:$A$244</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$243</f>
+              <f>'指标趋势'!$B$243:$B$244</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -1895,6 +1895,49 @@
         <ser>
           <idx val="1"/>
           <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!C242</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="triangle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$243:$A$244</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$C$243:$C$244</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!E242</f>
@@ -1929,8 +1972,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G242</f>
@@ -1965,8 +2008,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I242</f>
@@ -2008,7 +2051,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46308"/>
-          <min val="46306"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2050,7 +2093,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>s</a:t>
+                  <a:t>h</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2082,7 +2125,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.2 按名字找到板子</a:t>
+              <a:t>KR8.1 上电到出图</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2249,8 +2292,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2324,7 +2367,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.3 需要串口 (1=需要)</a:t>
+              <a:t>KR8.2 按名字找到板子</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2491,8 +2534,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
-          <min val="46306"/>
+          <max val="46309"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2534,7 +2577,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>是/否</a:t>
+                  <a:t>s</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2566,7 +2609,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR9.1 转子遥测可用 (1=可用)</a:t>
+              <a:t>KR8.3 需要串口 (1=需要)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2733,8 +2776,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2808,7 +2851,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR9.2 远程升级失败自动回滚 (1=有)</a:t>
+              <a:t>KR9.1 转子遥测可用 (1=可用)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3292,7 +3335,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR10.1 可实时播放内容数</a:t>
+              <a:t>KR9.2 远程升级失败自动回滚 (1=有)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3502,7 +3545,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>个</a:t>
+                  <a:t>是/否</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -3534,7 +3577,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR10.2 交互方式数</a:t>
+              <a:t>KR10.1 可实时播放内容数</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3744,7 +3787,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>种</a:t>
+                  <a:t>个</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -3765,6 +3808,248 @@
 </file>
 
 <file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>KR10.2 交互方式数</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <scatterStyle val="lineMarker"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!B361</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="2E75B6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$362</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$B$362</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!E361</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$D$362:$D$363</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$E$362:$E$363</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!G361</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$F$362:$F$363</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$G$362:$G$363</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!I361</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$H$362:$H$363</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$I$362:$I$363</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="46309"/>
+          <min val="46307"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日期</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="mm-dd" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>种</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="span"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -3953,7 +4238,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -5005,7 +5290,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR2.1 体帧率</a:t>
+              <a:t>KR1.6 内容刷新率 (实转上屏)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -5047,12 +5332,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$90:$A$92</f>
+              <f>'指标趋势'!$A$90</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$90:$B$92</f>
+              <f>'指标趋势'!$B$90</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5060,49 +5345,6 @@
         <ser>
           <idx val="1"/>
           <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!C89</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="triangle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="ED7D31"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$A$90:$A$92</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$C$90:$C$92</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!E89</f>
@@ -5137,8 +5379,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G89</f>
@@ -5173,8 +5415,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I89</f>
@@ -5216,7 +5458,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46308"/>
-          <min val="46238"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -5258,7 +5500,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Hz</a:t>
+                  <a:t>fps</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -5290,7 +5532,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR3.1 每面像素数</a:t>
+              <a:t>KR2.1 体帧率</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -5332,12 +5574,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$107:$A$108</f>
+              <f>'指标趋势'!$A$107:$A$109</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$107:$B$108</f>
+              <f>'指标趋势'!$B$107:$B$109</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5375,12 +5617,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$107:$A$108</f>
+              <f>'指标趋势'!$A$107:$A$109</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$107:$C$108</f>
+              <f>'指标趋势'!$C$107:$C$109</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5501,7 +5743,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46308"/>
-          <min val="46307"/>
+          <min val="46238"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -5543,7 +5785,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>px</a:t>
+                  <a:t>Hz</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -5575,7 +5817,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR3.2 每圈片数</a:t>
+              <a:t>KR3.1 每面像素数</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -5617,12 +5859,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$124:$A$127</f>
+              <f>'指标趋势'!$A$124:$A$125</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$124:$B$127</f>
+              <f>'指标趋势'!$B$124:$B$125</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5660,12 +5902,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$124:$A$127</f>
+              <f>'指标趋势'!$A$124:$A$125</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$124:$C$127</f>
+              <f>'指标趋势'!$C$124:$C$125</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5786,7 +6028,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46308"/>
-          <min val="46231"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -5828,7 +6070,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>片</a:t>
+                  <a:t>px</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -5860,7 +6102,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR4.1 色深</a:t>
+              <a:t>KR3.2 每圈片数</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -5902,12 +6144,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$141:$A$145</f>
+              <f>'指标趋势'!$A$141:$A$144</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$141:$B$145</f>
+              <f>'指标趋势'!$B$141:$B$144</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5945,12 +6187,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$141:$A$145</f>
+              <f>'指标趋势'!$A$141:$A$144</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$141:$C$145</f>
+              <f>'指标趋势'!$C$141:$C$144</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -6113,7 +6355,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>bit/通道</a:t>
+                  <a:t>片</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -6597,6 +6839,28 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>359</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="22" name="Chart 22"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId22"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -6943,7 +7207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7085,7 +7349,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>内容刷新率 (上屏)</t>
+          <t>内容刷新率 (假转, 管线能力)</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -7310,10 +7574,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
           <t>KR1.5</t>
@@ -7363,37 +7627,23 @@
       <c r="Q8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>体帧率达到 30 Hz</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>显示优化</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>✅ 达成当前期目标</t>
-        </is>
-      </c>
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>KR2.1</t>
+          <t>KR1.6</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>体帧率</t>
+          <t>内容刷新率 (实转上屏)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>fps</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -7402,7 +7652,7 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>21.7</v>
+        <v>10.8</v>
       </c>
       <c r="J9" s="7" t="n">
         <v>46307</v>
@@ -7413,13 +7663,13 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>21.7</v>
+        <v>10.8</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
@@ -7428,20 +7678,20 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md (D9 首次转起来 640–654 RPM)</t>
         </is>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>0.7233333333333333</v>
+        <v>0.7200000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>画面更清晰</t>
+          <t>体帧率达到 30 Hz</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -7456,17 +7706,17 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>每面像素数</t>
+          <t>体帧率</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -7475,7 +7725,7 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>28800</v>
+        <v>21.7</v>
       </c>
       <c r="J10" s="7" t="n">
         <v>46307</v>
@@ -7486,55 +7736,69 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>0.7233333333333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>画面更清晰</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>显示优化</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>KR3.1</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>每面像素数</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
         <v>28800</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>28800</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>41472</v>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
-        </is>
-      </c>
-      <c r="Q10" s="8" t="n">
-        <v>0.6944444444444444</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>KR3.2</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>每圈片数</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>片</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>142</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>46307</v>
@@ -7545,69 +7809,55 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
+        <v>28800</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>28800</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>41472</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>KR3.2</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>每圈片数</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>片</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
         <v>142</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>358</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>605</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>0.2347107438016529</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>颜色更丰富</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>显示优化</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>✅ 达成当前期目标</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>KR4.1</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>色深</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>bit/通道</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>3</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>46307</v>
@@ -7618,13 +7868,13 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>12</v>
+        <v>358</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>12</v>
+        <v>605</v>
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
@@ -7637,109 +7887,123 @@
         </is>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2347107438016529</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>颜色更丰富</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>显示优化</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>KR4.1</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>色深</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>bit/通道</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>46307</v>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>立体像不变形、两面对齐、无重影</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>几何</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>KR5.1</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>几何 LUT 复现正确 (1=逐字节复现)</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>是/否</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>越大越好</t>
         </is>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I14" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>46308</v>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>V0 2047</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 44ed2cd</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>KR5.2</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>左右镜像已核实 (1=已核)</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>是/否</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>46308</v>
@@ -7758,64 +8022,50 @@
       <c r="N14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O14" s="11" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
       <c r="Q14" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>左右镜像已核实 (1=已核)</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>亮度合适、停转不伤眼</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>显示优化</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>✅ 达成当前期目标</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>KR6.1</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>停转自动低亮 (1=有)</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>是/否</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="J15" s="7" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -7831,64 +8081,64 @@
       <c r="N15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>🔄</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 3bc5736</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>长时间稳定</t>
+          <t>亮度合适、停转不伤眼</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>稳定</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>🔄 进行中 / 未达标</t>
+          <t>显示优化</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR6.1</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>停转自动低亮 (1=有)</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>越小越好</t>
+          <t>越大越好</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
@@ -7896,13 +8146,13 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
@@ -7911,7 +8161,7 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 3bc5736</t>
         </is>
       </c>
       <c r="Q16" s="8" t="n">
@@ -7919,32 +8169,46 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
+      <c r="A17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>稳定</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>🔄 进行中 / 未达标</t>
+        </is>
+      </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>连续无故障运行时长</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>越大越好</t>
+          <t>越小越好</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="J17" s="7" t="n">
         <v>46308</v>
@@ -7955,154 +8219,154 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 596b191</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M17" s="3" t="n">
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>KR7.2</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>连续无故障运行时长</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N18" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="O18" s="11" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr">
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>dr1v90 596b191</t>
         </is>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="Q18" s="8" t="n">
         <v>0.007083333333333334</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
+    <row r="19">
+      <c r="A19" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>上电即用</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>运维</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>KR8.1</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>上电到出图</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>越小越好</t>
         </is>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I19" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="J19" s="7" t="n">
         <v>46307</v>
       </c>
-      <c r="K18" s="6" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>V0 2047</t>
         </is>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L19" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M19" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N19" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr">
+      <c r="P19" s="6" t="inlineStr">
         <is>
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>KR8.2</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>按名字找到板子</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>越小越好</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>46308</v>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>V0 2047</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
       <c r="Q19" s="8" t="n">
@@ -8110,23 +8374,23 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>KR8.3</t>
+          <t>KR8.2</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>需要串口 (1=需要)</t>
+          <t>按名字找到板子</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>s</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -8135,10 +8399,10 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -8146,13 +8410,13 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
@@ -8161,7 +8425,7 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 30d82f9</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
       <c r="Q20" s="8" t="n">
@@ -8169,32 +8433,18 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>转起来能看状态、能远程升级</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>运维</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>🔄 进行中 / 未达标</t>
-        </is>
-      </c>
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR8.3</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用)</t>
+          <t>需要串口 (1=需要)</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -8204,14 +8454,14 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>越大越好</t>
+          <t>越小越好</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
@@ -8219,41 +8469,55 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 30d82f9</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" s="11" t="inlineStr">
-        <is>
-          <t>🔄</t>
-        </is>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
+      <c r="A22" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>转起来能看状态、能远程升级</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>运维</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>🔄 进行中 / 未达标</t>
+        </is>
+      </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>KR9.2</t>
+          <t>KR9.1</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>远程升级失败自动回滚 (1=有)</t>
+          <t>转子遥测可用 (1=可用)</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -8301,37 +8565,23 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>能放更多内容</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>✅ 达成当前期目标</t>
-        </is>
-      </c>
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>KR10.1</t>
+          <t>KR9.2</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>可实时播放内容数</t>
+          <t>远程升级失败自动回滚 (1=有)</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -8340,7 +8590,7 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>46308</v>
@@ -8351,55 +8601,69 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="11" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/rotor-ops 05c4231</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>能放更多内容</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>KR10.1</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>可实时播放内容数</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 887491a (live_push/README.md)</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>KR10.2</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>交互方式数</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>种</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>46308</v>
@@ -8410,78 +8674,137 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 887491a (live_push/README.md)</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>KR10.2</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>交互方式数</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>种</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="J25" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N25" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="P24" s="6" t="inlineStr">
+      <c r="P25" s="6" t="inlineStr">
         <is>
           <t>dr1v90 live_push/README.md</t>
         </is>
       </c>
-      <c r="Q24" s="8" t="n">
+      <c r="Q25" s="8" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>达成当前期目标</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>进行中 / 未达标</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>无数据 / 未开始</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>退步 / 阻塞</t>
         </is>
@@ -8489,35 +8812,35 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D11:D12"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="D4:D8"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8529,7 +8852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I346"/>
+  <dimension ref="A1:I363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8551,7 +8874,7 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>KR1.1 内容刷新率 (上屏) (fps, 越大越好)</t>
+          <t>KR1.1 内容刷新率 (假转, 管线能力) (fps, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9435,7 @@
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>KR2.1 体帧率 (Hz, 越大越好)</t>
+          <t>KR1.6 内容刷新率 (实转上屏) (fps, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -9165,71 +9488,55 @@
     </row>
     <row r="90">
       <c r="A90" s="19" t="n">
-        <v>46238</v>
+        <v>46307</v>
       </c>
       <c r="B90" s="3" t="n">
-        <v>22.1</v>
+        <v>10.8</v>
       </c>
       <c r="C90" s="3" t="n"/>
       <c r="D90" s="19" t="n">
-        <v>46238</v>
+        <v>46306</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>21.7</v>
+        <v>10.8</v>
       </c>
       <c r="F90" s="19" t="n">
-        <v>46238</v>
+        <v>46306</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H90" s="19" t="n">
-        <v>46238</v>
+        <v>46306</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B91" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="C91" s="3" t="n"/>
       <c r="D91" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>21.7</v>
+        <v>10.8</v>
       </c>
       <c r="F91" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H91" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B92" s="3" t="n"/>
-      <c r="C92" s="3" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="17" t="inlineStr">
         <is>
-          <t>KR3.1 每面像素数 (px, 越大越好)</t>
+          <t>KR2.1 体帧率 (Hz, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -9282,62 +9589,71 @@
     </row>
     <row r="107">
       <c r="A107" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="B107" s="3" t="n">
-        <v>28800</v>
+        <v>22.1</v>
       </c>
       <c r="C107" s="3" t="n"/>
       <c r="D107" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>28800</v>
+        <v>21.7</v>
       </c>
       <c r="F107" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>28800</v>
+        <v>24</v>
       </c>
       <c r="H107" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>41472</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B108" s="3" t="n"/>
-      <c r="C108" s="3" t="n">
-        <v>28800</v>
-      </c>
+        <v>46307</v>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="C108" s="3" t="n"/>
       <c r="D108" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>28800</v>
+        <v>21.7</v>
       </c>
       <c r="F108" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>28800</v>
+        <v>24</v>
       </c>
       <c r="H108" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>41472</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B109" s="3" t="n"/>
+      <c r="C109" s="3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="17" t="inlineStr">
         <is>
-          <t>KR3.2 每圈片数 (片, 越大越好)</t>
+          <t>KR3.1 每面像素数 (px, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -9390,80 +9706,62 @@
     </row>
     <row r="124">
       <c r="A124" s="19" t="n">
-        <v>46231</v>
+        <v>46307</v>
       </c>
       <c r="B124" s="3" t="n">
-        <v>360</v>
+        <v>28800</v>
       </c>
       <c r="C124" s="3" t="n"/>
       <c r="D124" s="19" t="n">
-        <v>46231</v>
+        <v>46307</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>142</v>
+        <v>28800</v>
       </c>
       <c r="F124" s="19" t="n">
-        <v>46231</v>
+        <v>46307</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>358</v>
+        <v>28800</v>
       </c>
       <c r="H124" s="19" t="n">
-        <v>46231</v>
+        <v>46307</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>605</v>
+        <v>41472</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="19" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B125" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="C125" s="3" t="n"/>
+        <v>46308</v>
+      </c>
+      <c r="B125" s="3" t="n"/>
+      <c r="C125" s="3" t="n">
+        <v>28800</v>
+      </c>
       <c r="D125" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>142</v>
+        <v>28800</v>
       </c>
       <c r="F125" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>358</v>
+        <v>28800</v>
       </c>
       <c r="H125" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B126" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="C126" s="3" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B127" s="3" t="n"/>
-      <c r="C127" s="3" t="n">
-        <v>358</v>
+        <v>41472</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="17" t="inlineStr">
         <is>
-          <t>KR4.1 色深 (bit/通道, 越大越好)</t>
+          <t>KR3.2 每圈片数 (片, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -9519,86 +9817,77 @@
         <v>46231</v>
       </c>
       <c r="B141" s="3" t="n">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="C141" s="3" t="n"/>
       <c r="D141" s="19" t="n">
         <v>46231</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="F141" s="19" t="n">
         <v>46231</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>12</v>
+        <v>358</v>
       </c>
       <c r="H141" s="19" t="n">
         <v>46231</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>12</v>
+        <v>605</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="19" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B142" s="3" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="C142" s="3" t="n"/>
       <c r="D142" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="F142" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>12</v>
+        <v>358</v>
       </c>
       <c r="H142" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>12</v>
+        <v>605</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="19" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B143" s="3" t="n"/>
-      <c r="C143" s="3" t="n">
-        <v>12</v>
-      </c>
+        <v>46307</v>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="C143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B144" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C144" s="3" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B145" s="3" t="n"/>
-      <c r="C145" s="3" t="n">
-        <v>12</v>
+      <c r="B144" s="3" t="n"/>
+      <c r="C144" s="3" t="n">
+        <v>358</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="17" t="inlineStr">
         <is>
-          <t>KR5.1 几何 LUT 复现正确 (1=逐字节复现) (是/否, 越大越好)</t>
+          <t>KR4.1 色深 (bit/通道, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -9651,62 +9940,89 @@
     </row>
     <row r="158">
       <c r="A158" s="19" t="n">
-        <v>46238</v>
+        <v>46231</v>
       </c>
       <c r="B158" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C158" s="3" t="n"/>
       <c r="D158" s="19" t="n">
-        <v>46238</v>
+        <v>46231</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F158" s="19" t="n">
-        <v>46238</v>
+        <v>46231</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H158" s="19" t="n">
-        <v>46238</v>
+        <v>46231</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="19" t="n">
-        <v>46308</v>
+        <v>46254</v>
       </c>
       <c r="B159" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C159" s="3" t="n"/>
       <c r="D159" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F159" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H159" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="19" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B160" s="3" t="n"/>
+      <c r="C160" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" s="3" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B162" s="3" t="n"/>
+      <c r="C162" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="17" t="inlineStr">
         <is>
-          <t>KR5.2 左右镜像已核实 (1=已核) (是/否, 越大越好)</t>
+          <t>KR5.1 几何 LUT 复现正确 (1=逐字节复现) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -9759,46 +10075,53 @@
     </row>
     <row r="175">
       <c r="A175" s="19" t="n">
-        <v>46308</v>
+        <v>46238</v>
       </c>
       <c r="B175" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C175" s="3" t="n"/>
       <c r="D175" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="E175" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F175" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="G175" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H175" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="I175" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="176">
+      <c r="A176" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" s="3" t="n"/>
       <c r="D176" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E176" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F176" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G176" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H176" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>1</v>
@@ -9807,7 +10130,7 @@
     <row r="190">
       <c r="A190" s="17" t="inlineStr">
         <is>
-          <t>KR6.1 停转自动低亮 (1=有) (是/否, 越大越好)</t>
+          <t>KR5.2 左右镜像已核实 (1=已核) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -9860,26 +10183,26 @@
     </row>
     <row r="192">
       <c r="A192" s="19" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B192" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C192" s="3" t="n"/>
       <c r="D192" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E192" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F192" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="G192" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H192" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>1</v>
@@ -9887,19 +10210,19 @@
     </row>
     <row r="193">
       <c r="D193" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E193" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F193" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G193" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H193" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I193" s="3" t="n">
         <v>1</v>
@@ -9908,7 +10231,7 @@
     <row r="207">
       <c r="A207" s="17" t="inlineStr">
         <is>
-          <t>KR7.1 丢帧/迟到率 (%, 越小越好)</t>
+          <t>KR6.1 停转自动低亮 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -9961,57 +10284,55 @@
     </row>
     <row r="209">
       <c r="A209" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B209" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C209" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C209" s="3" t="n"/>
       <c r="D209" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F209" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H209" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
       <c r="D210" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F210" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H210" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="17" t="inlineStr">
         <is>
-          <t>KR7.2 连续无故障运行时长 (h, 越大越好)</t>
+          <t>KR7.1 丢帧/迟到率 (%, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -10064,62 +10385,57 @@
     </row>
     <row r="226">
       <c r="A226" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B226" s="3" t="n"/>
+        <v>46308</v>
+      </c>
+      <c r="B226" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C226" s="3" t="n">
-        <v>47.9</v>
+        <v>0</v>
       </c>
       <c r="D226" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F226" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>8</v>
+        <v>0.1</v>
       </c>
       <c r="H226" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>24</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B227" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="C227" s="3" t="n"/>
       <c r="D227" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F227" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>8</v>
+        <v>0.1</v>
       </c>
       <c r="H227" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>24</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="17" t="inlineStr">
         <is>
-          <t>KR8.1 上电到出图 (s, 越小越好)</t>
+          <t>KR7.2 连续无故障运行时长 (h, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10174,53 +10490,60 @@
       <c r="A243" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="B243" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="C243" s="3" t="n"/>
+      <c r="B243" s="3" t="n"/>
+      <c r="C243" s="3" t="n">
+        <v>47.9</v>
+      </c>
       <c r="D243" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E243" s="3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F243" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H243" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I243" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="244">
+      <c r="A244" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C244" s="3" t="n"/>
       <c r="D244" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E244" s="3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F244" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H244" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="17" t="inlineStr">
         <is>
-          <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
+          <t>KR8.1 上电到出图 (s, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -10273,55 +10596,55 @@
     </row>
     <row r="260">
       <c r="A260" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B260" s="3" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C260" s="3" t="n"/>
       <c r="D260" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="E260" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F260" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H260" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="I260" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="261">
       <c r="D261" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E261" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F261" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H261" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="17" t="inlineStr">
         <is>
-          <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
+          <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -10374,55 +10697,55 @@
     </row>
     <row r="277">
       <c r="A277" s="19" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B277" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C277" s="3" t="n"/>
       <c r="D277" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E277" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F277" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="G277" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H277" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I277" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="278">
       <c r="D278" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E278" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F278" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G278" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H278" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I278" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="17" t="inlineStr">
         <is>
-          <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
+          <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -10475,55 +10798,55 @@
     </row>
     <row r="294">
       <c r="A294" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B294" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C294" s="3" t="n"/>
       <c r="D294" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="E294" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F294" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H294" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="I294" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c r="D295" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E295" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F295" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G295" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H295" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I295" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="17" t="inlineStr">
         <is>
-          <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
+          <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10947,7 @@
     <row r="326">
       <c r="A326" s="17" t="inlineStr">
         <is>
-          <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
+          <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10680,26 +11003,26 @@
         <v>46308</v>
       </c>
       <c r="B328" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C328" s="3" t="n"/>
       <c r="D328" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E328" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F328" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H328" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I328" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -10707,25 +11030,25 @@
         <v>46309</v>
       </c>
       <c r="E329" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F329" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H329" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="I329" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="17" t="inlineStr">
         <is>
-          <t>KR10.2 交互方式数 (种, 越大越好)</t>
+          <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10781,26 +11104,26 @@
         <v>46308</v>
       </c>
       <c r="B345" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C345" s="3" t="n"/>
       <c r="D345" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E345" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F345" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H345" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I345" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="346">
@@ -10808,18 +11131,119 @@
         <v>46309</v>
       </c>
       <c r="E346" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F346" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="G346" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H346" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="I346" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="17" t="inlineStr">
+        <is>
+          <t>KR10.2 交互方式数 (种, 越大越好)</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="18" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B361" s="18" t="inlineStr">
+        <is>
+          <t>实测</t>
+        </is>
+      </c>
+      <c r="C361" s="18" t="inlineStr">
+        <is>
+          <t>仿真/台架</t>
+        </is>
+      </c>
+      <c r="D361" s="18" t="inlineStr">
+        <is>
+          <t>V0 目标 日期</t>
+        </is>
+      </c>
+      <c r="E361" s="18" t="inlineStr">
+        <is>
+          <t>V0 目标</t>
+        </is>
+      </c>
+      <c r="F361" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标 日期</t>
+        </is>
+      </c>
+      <c r="G361" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标</t>
+        </is>
+      </c>
+      <c r="H361" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标 日期</t>
+        </is>
+      </c>
+      <c r="I361" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B362" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C362" s="3" t="n"/>
+      <c r="D362" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E362" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F362" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G362" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H362" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="I362" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="D363" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E363" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F363" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G363" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H363" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I363" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11883,7 +12307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11958,7 +12382,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>内容刷新率 (上屏)</t>
+          <t>内容刷新率 (假转, 管线能力)</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -12040,7 +12464,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>内容刷新率 (上屏)</t>
+          <t>内容刷新率 (假转, 管线能力)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -12286,7 +12710,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>内容刷新率 (上屏)</t>
+          <t>内容刷新率 (假转, 管线能力)</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -12327,7 +12751,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>内容刷新率 (上屏)</t>
+          <t>内容刷新率 (假转, 管线能力)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -12409,7 +12833,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>内容刷新率 (上屏)</t>
+          <t>内容刷新率 (假转, 管线能力)</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -12655,7 +13079,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>内容刷新率 (上屏)</t>
+          <t>内容刷新率 (假转, 管线能力)</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -12696,7 +13120,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>内容刷新率 (上屏)</t>
+          <t>内容刷新率 (假转, 管线能力)</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -12892,25 +13316,25 @@
         <v>46307</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>KR2.1</t>
+          <t>KR1.6</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>体帧率</t>
+          <t>内容刷新率 (实转上屏)</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>fps</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>21.7</v>
+        <v>10.8</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -12919,12 +13343,12 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md (D9 首次转起来 640–654 RPM)</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>D9 DR1M90 首次转起来 640–654 RPM</t>
+          <t>由实转 ~650 RPM 推算 (= rps), 非逐帧计数</t>
         </is>
       </c>
     </row>
@@ -12933,25 +13357,25 @@
         <v>46307</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>每面像素数</t>
+          <t>体帧率</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>28800</v>
+        <v>21.7</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
@@ -12965,7 +13389,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>ICND2047 160×180</t>
+          <t>D9 DR1M90 首次转起来 640–654 RPM</t>
         </is>
       </c>
     </row>
@@ -12978,21 +13402,21 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>KR3.2</t>
+          <t>KR3.1</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>每圈片数</t>
+          <t>每面像素数</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>片</t>
+          <t>px</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>142</v>
+        <v>28800</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -13006,7 +13430,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>DR1M90 双面各 142 槽</t>
+          <t>ICND2047 160×180</t>
         </is>
       </c>
     </row>
@@ -13015,25 +13439,25 @@
         <v>46307</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>KR4.1</t>
+          <t>KR3.2</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>色深</t>
+          <t>每圈片数</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>bit/通道</t>
+          <t>片</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
@@ -13047,7 +13471,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>DR1M90 3-bit</t>
+          <t>DR1M90 双面各 142 槽</t>
         </is>
       </c>
     </row>
@@ -13056,25 +13480,25 @@
         <v>46307</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>KR6.1</t>
+          <t>KR4.1</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>停转自动低亮 (1=有)</t>
+          <t>色深</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>bit/通道</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -13083,12 +13507,12 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 3bc5736</t>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>停转低亮 0° 片上板通过并固化；4 次起停无 FAULT</t>
+          <t>DR1M90 3-bit</t>
         </is>
       </c>
     </row>
@@ -13097,39 +13521,39 @@
         <v>46307</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>KR6.1</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>连续无故障运行时长</t>
+          <t>停转自动低亮 (1=有)</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47.9</v>
+        <v>1</v>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_lane47_soak_verdict_1012.md</t>
+          <t>dr1v90 3bc5736</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>仅上行链路长跑 1.56e9 帧 0 错</t>
+          <t>停转低亮 0° 片上板通过并固化；4 次起停无 FAULT</t>
         </is>
       </c>
     </row>
@@ -13138,39 +13562,39 @@
         <v>46307</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>KR8.1</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>上电到出图</t>
+          <t>连续无故障运行时长</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>26</v>
+        <v>47.9</v>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
+          <t>claude_memory/project_lane47_soak_verdict_1012.md</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>重启后 uptime 26 s 转速门控亮起播 walking</t>
+          <t>仅上行链路长跑 1.56e9 帧 0 错</t>
         </is>
       </c>
     </row>
@@ -13183,21 +13607,21 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>KR8.3</t>
+          <t>KR8.1</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>需要串口 (1=需要)</t>
+          <t>上电到出图</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>s</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
@@ -13206,39 +13630,39 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 30d82f9</t>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>开机自连 WiFi 重启实测通过，用户拔掉串口</t>
+          <t>重启后 uptime 26 s 转速门控亮起播 walking</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>KR1.1</t>
+          <t>KR8.3</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>内容刷新率 (上屏)</t>
+          <t>需要串口 (1=需要)</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>fps</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
@@ -13247,12 +13671,12 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191 / 9bf16ad</t>
+          <t>dr1v90 30d82f9</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>主机实时推流 10 min：rx/切片/翻页 15.0 fps</t>
+          <t>开机自连 WiFi 重启实测通过，用户拔掉串口</t>
         </is>
       </c>
     </row>
@@ -13265,21 +13689,21 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>KR1.2</t>
+          <t>KR1.1</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>端到端延迟 p50</t>
+          <t>内容刷新率 (假转, 管线能力)</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>fps</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
@@ -13288,12 +13712,12 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a (live_push/README.md)</t>
+          <t>dr1v90 596b191 / 9bf16ad</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>第一次上板：停等发送 + --max-fps 15，未过</t>
+          <t>主机实时推流 10 min：rx/切片/翻页 15.0 fps</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13744,7 @@
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>84.7</v>
+        <v>114</v>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
@@ -13329,12 +13753,12 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 60c619a (live_push/README.md)</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>发送流水线 + --max-fps 0；p95 158 / p99 198 ms</t>
+          <t>第一次上板：停等发送 + --max-fps 15，未过</t>
         </is>
       </c>
     </row>
@@ -13361,7 +13785,7 @@
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>95</v>
+        <v>84.7</v>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
@@ -13370,12 +13794,12 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验</t>
+          <t>发送流水线 + --max-fps 0；p95 158 / p99 198 ms</t>
         </is>
       </c>
     </row>
@@ -13388,12 +13812,12 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>KR1.4</t>
+          <t>KR1.2</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>主机出帧耗时 p99</t>
+          <t>端到端延迟 p50</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -13402,7 +13826,7 @@
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
@@ -13411,12 +13835,12 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 887491a</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>voxlive 实时路径单帧 ~23 ms</t>
+          <t>主会话新克隆独立复验</t>
         </is>
       </c>
     </row>
@@ -13443,7 +13867,7 @@
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>20.3</v>
+        <v>23</v>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
@@ -13452,12 +13876,12 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 887491a</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>10 min 连续出帧 p99 18.7–20.3 ms</t>
+          <t>voxlive 实时路径单帧 ~23 ms</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13908,7 @@
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>22</v>
+        <v>20.3</v>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
@@ -13493,12 +13917,12 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>主会话独立复验 p99 22 ms</t>
+          <t>10 min 连续出帧 p99 18.7–20.3 ms</t>
         </is>
       </c>
     </row>
@@ -13511,12 +13935,12 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>KR1.5</t>
+          <t>KR1.4</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>板上切片耗时 (每帧)</t>
+          <t>主机出帧耗时 p99</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -13525,7 +13949,7 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>17.3</v>
+        <v>22</v>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
@@ -13534,12 +13958,12 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>groot 实时推流 (体素比 bonsai 少，内容不同)</t>
+          <t>主会话独立复验 p99 22 ms</t>
         </is>
       </c>
     </row>
@@ -13548,25 +13972,25 @@
         <v>46308</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>KR10.1</t>
+          <t>KR1.5</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>可实时播放内容数</t>
+          <t>板上切片耗时 (每帧)</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2</v>
+        <v>17.3</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
@@ -13575,12 +13999,12 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 887491a (live_push/README.md)</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>walking / groot 实时推流逐字节核过</t>
+          <t>groot 实时推流 (体素比 bonsai 少，内容不同)</t>
         </is>
       </c>
     </row>
@@ -13593,21 +14017,21 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>KR10.2</t>
+          <t>KR10.1</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>交互方式数</t>
+          <t>可实时播放内容数</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>种</t>
+          <t>个</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
@@ -13616,12 +14040,12 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 live_push/README.md</t>
+          <t>dr1v90 887491a (live_push/README.md)</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>--keys 键盘旋转/缩放</t>
+          <t>walking / groot 实时推流逐字节核过</t>
         </is>
       </c>
     </row>
@@ -13630,39 +14054,39 @@
         <v>46308</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>KR2.1</t>
+          <t>KR10.2</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>体帧率</t>
+          <t>交互方式数</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>种</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f</t>
+          <t>dr1v90 live_push/README.md</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>30 Hz 纯切片位流第一次上硅 (无屏)：切片链按 30 Hz 节拍跑通，尾部 late 0.2%</t>
+          <t>--keys 键盘旋转/缩放</t>
         </is>
       </c>
     </row>
@@ -13689,21 +14113,21 @@
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>仿真</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 71d006f</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>1 期桥 6 链 1串2 4296 片/s = 24 Hz×358 片 (余量 0.40%)</t>
+          <t>30 Hz 纯切片位流第一次上硅 (无屏)：切片链按 30 Hz 节拍跑通，尾部 late 0.2%</t>
         </is>
       </c>
     </row>
@@ -13712,25 +14136,25 @@
         <v>46308</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>每面像素数</t>
+          <t>体帧率</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>28800</v>
+        <v>24</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
@@ -13744,7 +14168,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>1 期 2260 验证板 160×180</t>
+          <t>1 期桥 6 链 1串2 4296 片/s = 24 Hz×358 片 (余量 0.40%)</t>
         </is>
       </c>
     </row>
@@ -13757,21 +14181,21 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>KR3.2</t>
+          <t>KR3.1</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>每圈片数</t>
+          <t>每面像素数</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>片</t>
+          <t>px</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>358</v>
+        <v>28800</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
@@ -13780,12 +14204,12 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 a9fc48c / cdf49c6</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>1 期 LUT 358 片 + 桥仿真</t>
+          <t>1 期 2260 验证板 160×180</t>
         </is>
       </c>
     </row>
@@ -13794,25 +14218,25 @@
         <v>46308</v>
       </c>
       <c r="B47" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>KR4.1</t>
+          <t>KR3.2</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>色深</t>
+          <t>每圈片数</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>bit/通道</t>
+          <t>片</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>12</v>
+        <v>358</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
@@ -13821,12 +14245,12 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 a9fc48c / cdf49c6</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>1 期桥 12-bit 整链仿真 PASS</t>
+          <t>1 期 LUT 358 片 + 桥仿真</t>
         </is>
       </c>
     </row>
@@ -13835,39 +14259,39 @@
         <v>46308</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>KR5.1</t>
+          <t>KR4.1</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
+          <t>色深</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>bit/通道</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
+          <t>1 期桥 12-bit 整链仿真 PASS</t>
         </is>
       </c>
     </row>
@@ -13880,12 +14304,12 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>KR5.1</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>左右镜像已核实 (1=已核)</t>
+          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -13894,7 +14318,7 @@
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
@@ -13903,12 +14327,12 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>2047 是否整体左右镜像未核</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
         </is>
       </c>
     </row>
@@ -13917,39 +14341,39 @@
         <v>46308</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>左右镜像已核实 (1=已核)</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
+          <t>2047 是否整体左右镜像未核</t>
         </is>
       </c>
     </row>
@@ -13976,7 +14400,7 @@
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
@@ -13985,12 +14409,12 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 473abcf</t>
+          <t>dr1v90 71d006f</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
+          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
         </is>
       </c>
     </row>
@@ -14021,17 +14445,17 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 473abcf</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>实时推流 624 s NAK 0 / forced 0</t>
+          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
         </is>
       </c>
     </row>
@@ -14044,21 +14468,21 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>连续无故障运行时长</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
@@ -14072,7 +14496,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>实时推流连续 624 s 无故障 (未做更长)</t>
+          <t>实时推流 624 s NAK 0 / forced 0</t>
         </is>
       </c>
     </row>
@@ -14081,25 +14505,25 @@
         <v>46308</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>按名字找到板子</t>
+          <t>连续无故障运行时长</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>34</v>
+        <v>0.17</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
@@ -14108,12 +14532,12 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>实时推流连续 624 s 无故障 (未做更长)</t>
         </is>
       </c>
     </row>
@@ -14122,25 +14546,25 @@
         <v>46308</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR8.2</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用)</t>
+          <t>按名字找到板子</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>s</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
@@ -14149,12 +14573,12 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
     </row>
@@ -14167,12 +14591,12 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>KR9.2</t>
+          <t>KR9.1</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>远程升级失败自动回滚 (1=有)</t>
+          <t>转子遥测可用 (1=可用)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -14195,12 +14619,53 @@
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
+          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>KR9.2</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>远程升级失败自动回滚 (1=有)</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/rotor-ops 05c4231</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
           <t>D7 返工中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I56"/>
+  <autoFilter ref="A1:I57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -14,7 +14,7 @@
     <sheet name="历史记录" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -95,12 +95,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -197,11 +197,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -829,7 +829,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR5.1 几何 LUT 复现正确 (1=逐字节复现)</a:t>
+              <a:t>KR4.2 链路色深 12-bit 已验证 (1=是)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -843,27 +843,27 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!B174</f>
+              <f>'指标趋势'!C174</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln w="22000">
               <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="triangle"/>
             <size val="7"/>
             <spPr>
               <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
               <a:ln>
                 <a:solidFill>
-                  <a:srgbClr val="2E75B6"/>
+                  <a:srgbClr val="ED7D31"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -871,12 +871,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$175:$A$176</f>
+              <f>'指标趋势'!$A$175</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$175:$B$176</f>
+              <f>'指标趋势'!$C$175</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -996,8 +996,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
-          <min val="46238"/>
+          <max val="46309"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1071,7 +1071,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR5.2 左右镜像已核实 (1=已核)</a:t>
+              <a:t>KR5.1 几何 LUT 复现正确 (1=逐字节复现)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1113,12 +1113,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$192</f>
+              <f>'指标趋势'!$A$192:$A$193</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$192</f>
+              <f>'指标趋势'!$B$192:$B$193</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -1238,8 +1238,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46238"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1313,7 +1313,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR6.1 停转自动低亮 (1=有)</a:t>
+              <a:t>KR5.2 左右镜像已核实 (1=已核)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1480,8 +1480,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
-          <min val="46306"/>
+          <max val="46309"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1555,7 +1555,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR7.1 丢帧/迟到率</a:t>
+              <a:t>KR6.1 停转自动低亮 (1=有)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1612,49 +1612,6 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!C225</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="triangle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="ED7D31"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$A$226</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$C$226</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
               <f>'指标趋势'!E225</f>
             </strRef>
           </tx>
@@ -1687,8 +1644,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G225</f>
@@ -1723,8 +1680,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I225</f>
@@ -1765,8 +1722,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1808,7 +1765,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>%</a:t>
+                  <a:t>是/否</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1840,7 +1797,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR7.2 连续无故障运行时长</a:t>
+              <a:t>KR7.1 丢帧/迟到率</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1882,12 +1839,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$243:$A$244</f>
+              <f>'指标趋势'!$A$243</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$243:$B$244</f>
+              <f>'指标趋势'!$B$243</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -1925,12 +1882,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$243:$A$244</f>
+              <f>'指标趋势'!$A$243</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$243:$C$244</f>
+              <f>'指标趋势'!$C$243</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -2050,7 +2007,7 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
+          <max val="46309"/>
           <min val="46307"/>
         </scaling>
         <delete val="0"/>
@@ -2093,7 +2050,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>h</a:t>
+                  <a:t>%</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2125,7 +2082,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.1 上电到出图</a:t>
+              <a:t>KR7.2 连续无故障运行时长</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2167,12 +2124,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$260</f>
+              <f>'指标趋势'!$A$260:$A$261</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$260</f>
+              <f>'指标趋势'!$B$260:$B$261</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -2180,6 +2137,49 @@
         <ser>
           <idx val="1"/>
           <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!C259</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="triangle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$260:$A$261</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$C$260:$C$261</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!E259</f>
@@ -2214,8 +2214,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G259</f>
@@ -2250,8 +2250,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I259</f>
@@ -2293,7 +2293,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46308"/>
-          <min val="46306"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2335,7 +2335,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>s</a:t>
+                  <a:t>h</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2367,7 +2367,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.2 按名字找到板子</a:t>
+              <a:t>KR8.1 上电到出图</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2534,8 +2534,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2609,7 +2609,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.3 需要串口 (1=需要)</a:t>
+              <a:t>KR8.2 按名字找到板子</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2776,8 +2776,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
-          <min val="46306"/>
+          <max val="46309"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2819,7 +2819,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>是/否</a:t>
+                  <a:t>s</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2851,7 +2851,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR9.1 转子遥测可用 (1=可用)</a:t>
+              <a:t>KR8.3 需要串口 (1=需要)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3018,8 +3018,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3335,7 +3335,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR9.2 远程升级失败自动回滚 (1=有)</a:t>
+              <a:t>KR9.1 转子遥测可用 (1=可用)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3577,7 +3577,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR10.1 可实时播放内容数</a:t>
+              <a:t>KR9.2 远程升级失败自动回滚 (1=有)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3787,7 +3787,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>个</a:t>
+                  <a:t>是/否</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -3819,7 +3819,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR10.2 交互方式数</a:t>
+              <a:t>KR10.1 可实时播放内容数</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4029,7 +4029,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>种</a:t>
+                  <a:t>个</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -4050,6 +4050,248 @@
 </file>
 
 <file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>KR10.2 交互方式数</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <scatterStyle val="lineMarker"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!B378</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="2E75B6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$379</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$B$379</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!E378</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$D$379:$D$380</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$E$379:$E$380</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!G378</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$F$379:$F$380</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$G$379:$G$380</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!I378</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$H$379:$H$380</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$I$379:$I$380</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="46309"/>
+          <min val="46307"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日期</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="mm-dd" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>种</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="span"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -4238,7 +4480,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -6861,6 +7103,28 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>376</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="23" name="Chart 23"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId23"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -7207,7 +7471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7904,9 +8168,9 @@
           <t>显示优化</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>✅ 达成当前期目标</t>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>⏸ 无数据 / 未开始</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -7964,32 +8228,18 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>立体像不变形、两面对齐、无重影</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>几何</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>🔄 进行中 / 未达标</t>
-        </is>
-      </c>
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>KR5.1</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
+          <t>链路色深 12-bit 已验证 (1=是)</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -8010,7 +8260,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="L14" s="3" t="n">
@@ -8022,14 +8272,14 @@
       <c r="N14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>⏸</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 cdf49c6 (gw5a_bridge/p1 verify ALL PASS)</t>
         </is>
       </c>
       <c r="Q14" s="8" t="n">
@@ -8037,18 +8287,32 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
+      <c r="A15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>立体像不变形、两面对齐、无重影</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>几何</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>🔄 进行中 / 未达标</t>
+        </is>
+      </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>KR5.1</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>左右镜像已核实 (1=已核)</t>
+          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -8062,7 +8326,7 @@
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>46308</v>
@@ -8081,64 +8345,50 @@
       <c r="N15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="11" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
       <c r="Q15" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>左右镜像已核实 (1=已核)</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>亮度合适、停转不伤眼</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>显示优化</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>✅ 达成当前期目标</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>KR6.1</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>停转自动低亮 (1=有)</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>是/否</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="J16" s="7" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
@@ -8154,64 +8404,64 @@
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 3bc5736</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>长时间稳定</t>
+          <t>亮度合适、停转不伤眼</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>稳定</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>🔄 进行中 / 未达标</t>
+          <t>显示优化</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR6.1</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>停转自动低亮 (1=有)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>越小越好</t>
+          <t>越大越好</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
@@ -8219,13 +8469,13 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
@@ -8234,7 +8484,7 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 3bc5736</t>
         </is>
       </c>
       <c r="Q17" s="8" t="n">
@@ -8242,32 +8492,46 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="A18" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>稳定</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>🔄 进行中 / 未达标</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>连续无故障运行时长</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>越大越好</t>
+          <t>越小越好</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="J18" s="7" t="n">
         <v>46308</v>
@@ -8278,154 +8542,154 @@
         </is>
       </c>
       <c r="L18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 596b191</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M18" s="3" t="n">
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>KR7.2</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>连续无故障运行时长</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N19" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="O18" s="11" t="inlineStr">
+      <c r="O19" s="12" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr">
+      <c r="P19" s="6" t="inlineStr">
         <is>
           <t>dr1v90 596b191</t>
         </is>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="Q19" s="8" t="n">
         <v>0.007083333333333334</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
+    <row r="20">
+      <c r="A20" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>上电即用</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>运维</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>KR8.1</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>上电到出图</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>越小越好</t>
         </is>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I20" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J20" s="7" t="n">
         <v>46307</v>
       </c>
-      <c r="K19" s="6" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>V0 2047</t>
         </is>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L20" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M20" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N20" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr">
+      <c r="P20" s="6" t="inlineStr">
         <is>
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>KR8.2</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>按名字找到板子</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>越小越好</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>46308</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>V0 2047</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
       <c r="Q20" s="8" t="n">
@@ -8433,23 +8697,23 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>KR8.3</t>
+          <t>KR8.2</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>需要串口 (1=需要)</t>
+          <t>按名字找到板子</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>s</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -8458,10 +8722,10 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
@@ -8469,13 +8733,13 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
@@ -8484,7 +8748,7 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 30d82f9</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
       <c r="Q21" s="8" t="n">
@@ -8492,32 +8756,18 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>转起来能看状态、能远程升级</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>运维</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>🔄 进行中 / 未达标</t>
-        </is>
-      </c>
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR8.3</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用)</t>
+          <t>需要串口 (1=需要)</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -8527,14 +8777,14 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>越大越好</t>
+          <t>越小越好</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
@@ -8542,41 +8792,55 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 30d82f9</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="11" t="inlineStr">
-        <is>
-          <t>🔄</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="A23" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>转起来能看状态、能远程升级</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>运维</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>🔄 进行中 / 未达标</t>
+        </is>
+      </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>KR9.2</t>
+          <t>KR9.1</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>远程升级失败自动回滚 (1=有)</t>
+          <t>转子遥测可用 (1=可用)</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -8609,7 +8873,7 @@
       <c r="N23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O23" s="11" t="inlineStr">
+      <c r="O23" s="12" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -8624,37 +8888,23 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>能放更多内容</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>✅ 达成当前期目标</t>
-        </is>
-      </c>
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>KR10.1</t>
+          <t>KR9.2</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>可实时播放内容数</t>
+          <t>远程升级失败自动回滚 (1=有)</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -8663,7 +8913,7 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>46308</v>
@@ -8674,55 +8924,69 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/rotor-ops 05c4231</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>能放更多内容</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>KR10.1</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>可实时播放内容数</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 887491a (live_push/README.md)</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>KR10.2</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>交互方式数</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>种</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>46308</v>
@@ -8733,114 +8997,177 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 887491a (live_push/README.md)</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>KR10.2</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>交互方式数</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>种</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="J26" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr">
+      <c r="P26" s="6" t="inlineStr">
         <is>
           <t>dr1v90 live_push/README.md</t>
         </is>
       </c>
-      <c r="Q25" s="8" t="n">
+      <c r="Q26" s="8" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>达成当前期目标</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>进行中 / 未达标</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>无数据 / 未开始</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>退步 / 阻塞</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="33">
     <mergeCell ref="B4:B9"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C24:C25"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B23:B24"/>
     <mergeCell ref="C4:C9"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="C25:C26"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C23:C24"/>
     <mergeCell ref="D4:D9"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C18:C19"/>
     <mergeCell ref="A11:A12"/>
-    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8852,7 +9179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I363"/>
+  <dimension ref="A1:I380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10022,7 +10349,7 @@
     <row r="173">
       <c r="A173" s="17" t="inlineStr">
         <is>
-          <t>KR5.1 几何 LUT 复现正确 (1=逐字节复现) (是/否, 越大越好)</t>
+          <t>KR4.2 链路色深 12-bit 已验证 (1=是) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10075,53 +10402,46 @@
     </row>
     <row r="175">
       <c r="A175" s="19" t="n">
-        <v>46238</v>
-      </c>
-      <c r="B175" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B175" s="3" t="n"/>
+      <c r="C175" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C175" s="3" t="n"/>
       <c r="D175" s="19" t="n">
-        <v>46238</v>
+        <v>46307</v>
       </c>
       <c r="E175" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F175" s="19" t="n">
-        <v>46238</v>
+        <v>46307</v>
       </c>
       <c r="G175" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H175" s="19" t="n">
-        <v>46238</v>
+        <v>46307</v>
       </c>
       <c r="I175" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B176" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C176" s="3" t="n"/>
       <c r="D176" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E176" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F176" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G176" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H176" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>1</v>
@@ -10130,7 +10450,7 @@
     <row r="190">
       <c r="A190" s="17" t="inlineStr">
         <is>
-          <t>KR5.2 左右镜像已核实 (1=已核) (是/否, 越大越好)</t>
+          <t>KR5.1 几何 LUT 复现正确 (1=逐字节复现) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10183,46 +10503,53 @@
     </row>
     <row r="192">
       <c r="A192" s="19" t="n">
-        <v>46308</v>
+        <v>46238</v>
       </c>
       <c r="B192" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C192" s="3" t="n"/>
       <c r="D192" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="E192" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F192" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="G192" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H192" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="193">
+      <c r="A193" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" s="3" t="n"/>
       <c r="D193" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E193" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F193" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G193" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H193" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I193" s="3" t="n">
         <v>1</v>
@@ -10231,7 +10558,7 @@
     <row r="207">
       <c r="A207" s="17" t="inlineStr">
         <is>
-          <t>KR6.1 停转自动低亮 (1=有) (是/否, 越大越好)</t>
+          <t>KR5.2 左右镜像已核实 (1=已核) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10284,26 +10611,26 @@
     </row>
     <row r="209">
       <c r="A209" s="19" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B209" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C209" s="3" t="n"/>
       <c r="D209" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E209" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F209" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="G209" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H209" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I209" s="3" t="n">
         <v>1</v>
@@ -10311,19 +10638,19 @@
     </row>
     <row r="210">
       <c r="D210" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E210" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F210" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G210" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H210" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>1</v>
@@ -10332,7 +10659,7 @@
     <row r="224">
       <c r="A224" s="17" t="inlineStr">
         <is>
-          <t>KR7.1 丢帧/迟到率 (%, 越小越好)</t>
+          <t>KR6.1 停转自动低亮 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10385,57 +10712,55 @@
     </row>
     <row r="226">
       <c r="A226" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B226" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C226" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C226" s="3" t="n"/>
       <c r="D226" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F226" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H226" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="D227" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F227" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H227" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="17" t="inlineStr">
         <is>
-          <t>KR7.2 连续无故障运行时长 (h, 越大越好)</t>
+          <t>KR7.1 丢帧/迟到率 (%, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -10488,62 +10813,57 @@
     </row>
     <row r="243">
       <c r="A243" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B243" s="3" t="n"/>
+        <v>46308</v>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C243" s="3" t="n">
-        <v>47.9</v>
+        <v>0</v>
       </c>
       <c r="D243" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E243" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F243" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>8</v>
+        <v>0.1</v>
       </c>
       <c r="H243" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I243" s="3" t="n">
-        <v>24</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B244" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="C244" s="3" t="n"/>
       <c r="D244" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E244" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F244" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>8</v>
+        <v>0.1</v>
       </c>
       <c r="H244" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>24</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="17" t="inlineStr">
         <is>
-          <t>KR8.1 上电到出图 (s, 越小越好)</t>
+          <t>KR7.2 连续无故障运行时长 (h, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10598,53 +10918,60 @@
       <c r="A260" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="B260" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="C260" s="3" t="n"/>
+      <c r="B260" s="3" t="n"/>
+      <c r="C260" s="3" t="n">
+        <v>47.9</v>
+      </c>
       <c r="D260" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E260" s="3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F260" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H260" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I260" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="261">
+      <c r="A261" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B261" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C261" s="3" t="n"/>
       <c r="D261" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E261" s="3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F261" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H261" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="17" t="inlineStr">
         <is>
-          <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
+          <t>KR8.1 上电到出图 (s, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -10697,55 +11024,55 @@
     </row>
     <row r="277">
       <c r="A277" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B277" s="3" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C277" s="3" t="n"/>
       <c r="D277" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="E277" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F277" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="G277" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H277" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="I277" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="278">
       <c r="D278" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E278" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F278" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G278" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H278" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I278" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="17" t="inlineStr">
         <is>
-          <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
+          <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -10798,55 +11125,55 @@
     </row>
     <row r="294">
       <c r="A294" s="19" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B294" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C294" s="3" t="n"/>
       <c r="D294" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E294" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F294" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H294" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I294" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="295">
       <c r="D295" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E295" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F295" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G295" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H295" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I295" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="17" t="inlineStr">
         <is>
-          <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
+          <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -10899,55 +11226,55 @@
     </row>
     <row r="311">
       <c r="A311" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B311" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C311" s="3" t="n"/>
       <c r="D311" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="E311" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F311" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="G311" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H311" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="I311" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
       <c r="D312" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E312" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F312" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G312" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H312" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I312" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="17" t="inlineStr">
         <is>
-          <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
+          <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11375,7 @@
     <row r="343">
       <c r="A343" s="17" t="inlineStr">
         <is>
-          <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
+          <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -11104,26 +11431,26 @@
         <v>46308</v>
       </c>
       <c r="B345" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C345" s="3" t="n"/>
       <c r="D345" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E345" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F345" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H345" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I345" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -11131,25 +11458,25 @@
         <v>46309</v>
       </c>
       <c r="E346" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F346" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="G346" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H346" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="I346" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="17" t="inlineStr">
         <is>
-          <t>KR10.2 交互方式数 (种, 越大越好)</t>
+          <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -11205,26 +11532,26 @@
         <v>46308</v>
       </c>
       <c r="B362" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C362" s="3" t="n"/>
       <c r="D362" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E362" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F362" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="G362" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H362" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I362" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="363">
@@ -11232,18 +11559,119 @@
         <v>46309</v>
       </c>
       <c r="E363" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F363" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="G363" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H363" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="I363" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="17" t="inlineStr">
+        <is>
+          <t>KR10.2 交互方式数 (种, 越大越好)</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="18" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B378" s="18" t="inlineStr">
+        <is>
+          <t>实测</t>
+        </is>
+      </c>
+      <c r="C378" s="18" t="inlineStr">
+        <is>
+          <t>仿真/台架</t>
+        </is>
+      </c>
+      <c r="D378" s="18" t="inlineStr">
+        <is>
+          <t>V0 目标 日期</t>
+        </is>
+      </c>
+      <c r="E378" s="18" t="inlineStr">
+        <is>
+          <t>V0 目标</t>
+        </is>
+      </c>
+      <c r="F378" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标 日期</t>
+        </is>
+      </c>
+      <c r="G378" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标</t>
+        </is>
+      </c>
+      <c r="H378" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标 日期</t>
+        </is>
+      </c>
+      <c r="I378" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B379" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C379" s="3" t="n"/>
+      <c r="D379" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E379" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F379" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G379" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H379" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="I379" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="D380" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E380" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F380" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G380" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H380" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I380" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11836,7 +12264,7 @@
         <v>46311</v>
       </c>
       <c r="F33" s="7" t="n"/>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11872,7 +12300,7 @@
         <v>46311</v>
       </c>
       <c r="F34" s="7" t="n"/>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11908,7 +12336,7 @@
         <v>46311</v>
       </c>
       <c r="F35" s="7" t="n"/>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12020,7 +12448,7 @@
         <v>46312</v>
       </c>
       <c r="F38" s="7" t="n"/>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12056,7 +12484,7 @@
         <v>46315</v>
       </c>
       <c r="F39" s="7" t="n"/>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -12092,7 +12520,7 @@
         <v>46317</v>
       </c>
       <c r="F40" s="7" t="n"/>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -12128,7 +12556,7 @@
         <v>46317</v>
       </c>
       <c r="F41" s="7" t="n"/>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -12164,7 +12592,7 @@
         <v>46319</v>
       </c>
       <c r="F42" s="7" t="n"/>
-      <c r="G42" s="14" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -12273,7 +12701,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>对角线 (y = x)</t>
         </is>
@@ -12307,7 +12735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -14300,16 +14728,16 @@
         <v>46308</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>KR5.1</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
+          <t>链路色深 12-bit 已验证 (1=是)</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -14322,17 +14750,17 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 cdf49c6 (gw5a_bridge/p1 verify ALL PASS)</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
+          <t>仅桥→2260 段仿真; 主控→桥→2260 全链未验</t>
         </is>
       </c>
     </row>
@@ -14345,12 +14773,12 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>KR5.1</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>左右镜像已核实 (1=已核)</t>
+          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -14359,7 +14787,7 @@
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
@@ -14368,12 +14796,12 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>2047 是否整体左右镜像未核</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
         </is>
       </c>
     </row>
@@ -14382,39 +14810,39 @@
         <v>46308</v>
       </c>
       <c r="B51" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>左右镜像已核实 (1=已核)</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
+          <t>2047 是否整体左右镜像未核</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14869,7 @@
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
@@ -14450,12 +14878,12 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 473abcf</t>
+          <t>dr1v90 71d006f</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
+          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
         </is>
       </c>
     </row>
@@ -14486,17 +14914,17 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 473abcf</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>实时推流 624 s NAK 0 / forced 0</t>
+          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
         </is>
       </c>
     </row>
@@ -14509,21 +14937,21 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>连续无故障运行时长</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
@@ -14537,7 +14965,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>实时推流连续 624 s 无故障 (未做更长)</t>
+          <t>实时推流 624 s NAK 0 / forced 0</t>
         </is>
       </c>
     </row>
@@ -14546,25 +14974,25 @@
         <v>46308</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>按名字找到板子</t>
+          <t>连续无故障运行时长</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>34</v>
+        <v>0.17</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
@@ -14573,12 +15001,12 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>实时推流连续 624 s 无故障 (未做更长)</t>
         </is>
       </c>
     </row>
@@ -14587,25 +15015,25 @@
         <v>46308</v>
       </c>
       <c r="B56" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR8.2</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用)</t>
+          <t>按名字找到板子</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>s</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
@@ -14614,12 +15042,12 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
     </row>
@@ -14632,12 +15060,12 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>KR9.2</t>
+          <t>KR9.1</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>远程升级失败自动回滚 (1=有)</t>
+          <t>转子遥测可用 (1=可用)</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -14660,12 +15088,53 @@
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
+          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>KR9.2</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>远程升级失败自动回滚 (1=有)</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/rotor-ops 05c4231</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
           <t>D7 返工中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I57"/>
+  <autoFilter ref="A1:I58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -11687,7 +11687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11731,7 +11731,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
@@ -11745,7 +11745,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>7</v>
@@ -11759,7 +11759,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>8</v>
@@ -11771,7 +11771,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>9</v>
@@ -11783,7 +11783,7 @@
         <v>46311</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>12</v>
@@ -11795,7 +11795,7 @@
         <v>46312</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>14</v>
@@ -11807,7 +11807,7 @@
         <v>46313</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>14</v>
@@ -11819,7 +11819,7 @@
         <v>46314</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>14</v>
@@ -11831,7 +11831,7 @@
         <v>46315</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>15</v>
@@ -11843,7 +11843,7 @@
         <v>46316</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>15</v>
@@ -11855,7 +11855,7 @@
         <v>46317</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>17</v>
@@ -11867,7 +11867,7 @@
         <v>46318</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>17</v>
@@ -11879,7 +11879,7 @@
         <v>46319</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>18</v>
@@ -12600,6 +12600,40 @@
       <c r="H42" s="6" t="inlineStr">
         <is>
           <t>待派 (需用户接线一次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>启动阶段屏显 (停转 0° 片当平面屏: ①PL 静态 logo ②启动状态逐行显示, 走公共片流 ③转稳切正常内容)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>8;9</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>⏸ backlog 未派</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>用户 10-13 定只记录; 与 D7 最近</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -14,7 +14,7 @@
     <sheet name="历史记录" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,7 +544,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR4.1 色深</a:t>
+              <a:t>KR3.2 每圈片数</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -586,12 +586,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$158:$A$162</f>
+              <f>'指标趋势'!$A$158:$A$161</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$158:$B$162</f>
+              <f>'指标趋势'!$B$158:$B$161</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -629,12 +629,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$158:$A$162</f>
+              <f>'指标趋势'!$A$158:$A$161</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$158:$C$162</f>
+              <f>'指标趋势'!$C$158:$C$161</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -797,7 +797,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>bit/通道</a:t>
+                  <a:t>片</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -829,7 +829,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR4.2 链路色深 12-bit 已验证 (1=是)</a:t>
+              <a:t>KR4.1 色深</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -841,6 +841,49 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!B174</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="2E75B6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$175:$A$179</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$B$175:$B$179</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
           <tx>
             <strRef>
               <f>'指标趋势'!C174</f>
@@ -871,19 +914,19 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$175</f>
+              <f>'指标趋势'!$A$175:$A$179</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$175</f>
+              <f>'指标趋势'!$C$175:$C$179</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!E174</f>
@@ -918,8 +961,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G174</f>
@@ -954,8 +997,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I174</f>
@@ -996,8 +1039,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46231"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1039,7 +1082,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>是/否</a:t>
+                  <a:t>bit/通道</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1071,7 +1114,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR5.1 几何 LUT 复现正确 (1=逐字节复现)</a:t>
+              <a:t>KR4.2 链路色深 12-bit 已验证 (1=是)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1085,27 +1128,27 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!B191</f>
+              <f>'指标趋势'!C191</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln w="22000">
               <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
+            <symbol val="triangle"/>
             <size val="7"/>
             <spPr>
               <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
+                <a:srgbClr val="ED7D31"/>
               </a:solidFill>
               <a:ln>
                 <a:solidFill>
-                  <a:srgbClr val="2E75B6"/>
+                  <a:srgbClr val="ED7D31"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1113,12 +1156,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$192:$A$193</f>
+              <f>'指标趋势'!$A$192</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$192:$B$193</f>
+              <f>'指标趋势'!$C$192</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -1238,8 +1281,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
-          <min val="46238"/>
+          <max val="46309"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1313,7 +1356,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR5.2 左右镜像已核实 (1=已核)</a:t>
+              <a:t>KR5.1 几何 LUT 复现正确 (1=逐字节复现)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1355,12 +1398,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$209</f>
+              <f>'指标趋势'!$A$209:$A$210</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$209</f>
+              <f>'指标趋势'!$B$209:$B$210</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -1480,8 +1523,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46238"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1555,7 +1598,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR6.1 停转自动低亮 (1=有)</a:t>
+              <a:t>KR5.2 左右镜像已核实 (1=已核)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1722,8 +1765,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
-          <min val="46306"/>
+          <max val="46309"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1797,7 +1840,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR7.1 丢帧/迟到率</a:t>
+              <a:t>KR6.1 停转自动低亮 (1=有)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1854,49 +1897,6 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!C242</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="triangle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="ED7D31"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$A$243</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$C$243</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
               <f>'指标趋势'!E242</f>
             </strRef>
           </tx>
@@ -1929,8 +1929,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G242</f>
@@ -1965,8 +1965,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I242</f>
@@ -2007,8 +2007,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2050,7 +2050,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>%</a:t>
+                  <a:t>是/否</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2082,7 +2082,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR7.2 连续无故障运行时长</a:t>
+              <a:t>KR7.1 丢帧/迟到率</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2124,12 +2124,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$260:$A$261</f>
+              <f>'指标趋势'!$A$260</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$260:$B$261</f>
+              <f>'指标趋势'!$B$260</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -2167,12 +2167,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$260:$A$261</f>
+              <f>'指标趋势'!$A$260</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$260:$C$261</f>
+              <f>'指标趋势'!$C$260</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -2292,7 +2292,7 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
+          <max val="46309"/>
           <min val="46307"/>
         </scaling>
         <delete val="0"/>
@@ -2335,7 +2335,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>h</a:t>
+                  <a:t>%</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2367,7 +2367,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.1 上电到出图</a:t>
+              <a:t>KR7.2 连续无故障: 软件链路 (假转, 无人值守)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2409,12 +2409,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$277</f>
+              <f>'指标趋势'!$A$277:$A$278</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$277</f>
+              <f>'指标趋势'!$B$277:$B$278</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -2422,6 +2422,49 @@
         <ser>
           <idx val="1"/>
           <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!C276</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="triangle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$277:$A$278</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$C$277:$C$278</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!E276</f>
@@ -2456,8 +2499,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G276</f>
@@ -2492,8 +2535,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I276</f>
@@ -2535,7 +2578,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46308"/>
-          <min val="46306"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2577,7 +2620,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>s</a:t>
+                  <a:t>h</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2609,7 +2652,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.2 按名字找到板子</a:t>
+              <a:t>KR8.4 上电到转稳全亮</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2661,114 +2704,6 @@
           </yVal>
           <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!E293</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="70AD47"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$D$294:$D$295</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$E$294:$E$295</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!G293</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$F$294:$F$295</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$G$294:$G$295</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!I293</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$H$294:$H$295</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$I$294:$I$295</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -2776,8 +2711,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2851,7 +2786,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.3 需要串口 (1=需要)</a:t>
+              <a:t>KR8.2 按名字找到板子</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3018,8 +2953,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
-          <min val="46306"/>
+          <max val="46309"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3061,7 +2996,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>是/否</a:t>
+                  <a:t>s</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -3335,7 +3270,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR9.1 转子遥测可用 (1=可用)</a:t>
+              <a:t>KR8.3 需要串口 (1=需要)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3502,8 +3437,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3577,7 +3512,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR9.2 远程升级失败自动回滚 (1=有)</a:t>
+              <a:t>KR9.1 转子遥测可用 (1=可用)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3819,7 +3754,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR10.1 可实时播放内容数</a:t>
+              <a:t>KR9.2 远程升级失败自动回滚 (1=有)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4029,7 +3964,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>个</a:t>
+                  <a:t>是/否</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -4061,7 +3996,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR10.2 交互方式数</a:t>
+              <a:t>KR10.1 可实时播放内容数</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4271,7 +4206,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>种</a:t>
+                  <a:t>个</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -4292,6 +4227,248 @@
 </file>
 
 <file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>KR10.2 交互方式数</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <scatterStyle val="lineMarker"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!B395</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="2E75B6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$396</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$B$396</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!E395</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$D$396:$D$397</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$E$396:$E$397</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!G395</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$F$396:$F$397</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$G$396:$G$397</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!I395</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$H$396:$H$397</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$I$396:$I$397</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="46309"/>
+          <min val="46307"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日期</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="mm-dd" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>种</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="span"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -4480,7 +4657,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -4878,7 +5055,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR1.3 WiFi 可用带宽</a:t>
+              <a:t>KR1.7 端到端延迟抖动 p99</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4920,12 +5097,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$39:$A$43</f>
+              <f>'指标趋势'!$A$39</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$39:$B$43</f>
+              <f>'指标趋势'!$B$39</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5045,8 +5222,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46307"/>
-          <min val="46157"/>
+          <max val="46309"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -5088,7 +5265,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Mbit/s</a:t>
+                  <a:t>ms</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -5120,7 +5297,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR1.4 主机出帧耗时 p99</a:t>
+              <a:t>KR1.3 WiFi 可用带宽</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -5162,12 +5339,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$56:$A$57</f>
+              <f>'指标趋势'!$A$56:$A$60</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$56:$B$57</f>
+              <f>'指标趋势'!$B$56:$B$60</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5287,8 +5464,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
-          <min val="46307"/>
+          <max val="46307"/>
+          <min val="46157"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -5330,7 +5507,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>ms</a:t>
+                  <a:t>Mbit/s</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -5362,7 +5539,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR1.5 板上切片耗时 (每帧)</a:t>
+              <a:t>KR1.4 主机出帧耗时 p99</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -5446,6 +5623,78 @@
           <yVal>
             <numRef>
               <f>'指标趋势'!$E$73:$E$74</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!G72</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$F$73:$F$74</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$G$73:$G$74</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!I72</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$H$73:$H$74</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$I$73:$I$74</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5532,7 +5781,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR1.6 内容刷新率 (实转上屏)</a:t>
+              <a:t>KR1.5 板上切片耗时 (每帧)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -5574,12 +5823,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$90</f>
+              <f>'指标趋势'!$A$90:$A$91</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$90</f>
+              <f>'指标趋势'!$B$90:$B$91</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5620,78 +5869,6 @@
           </yVal>
           <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!G89</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$F$90:$F$91</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$G$90:$G$91</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!I89</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$H$90:$H$91</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$I$90:$I$91</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -5700,7 +5877,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46308"/>
-          <min val="46306"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -5742,7 +5919,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>fps</a:t>
+                  <a:t>ms</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -5774,7 +5951,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR2.1 体帧率</a:t>
+              <a:t>KR1.6 内容刷新率 (实转上屏)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -5816,12 +5993,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$107:$A$109</f>
+              <f>'指标趋势'!$A$107</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$107:$B$109</f>
+              <f>'指标趋势'!$B$107</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -5829,49 +6006,6 @@
         <ser>
           <idx val="1"/>
           <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!C106</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="triangle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="ED7D31"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$A$107:$A$109</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$C$107:$C$109</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!E106</f>
@@ -5906,8 +6040,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G106</f>
@@ -5942,8 +6076,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I106</f>
@@ -5985,7 +6119,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46308"/>
-          <min val="46238"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -6027,7 +6161,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Hz</a:t>
+                  <a:t>fps</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -6059,7 +6193,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR3.1 每面像素数</a:t>
+              <a:t>KR2.1 体帧率</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -6101,12 +6235,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$124:$A$125</f>
+              <f>'指标趋势'!$A$124:$A$126</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$124:$B$125</f>
+              <f>'指标趋势'!$B$124:$B$126</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -6144,12 +6278,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$124:$A$125</f>
+              <f>'指标趋势'!$A$124:$A$126</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$124:$C$125</f>
+              <f>'指标趋势'!$C$124:$C$126</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -6270,7 +6404,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46308"/>
-          <min val="46307"/>
+          <min val="46238"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -6312,7 +6446,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>px</a:t>
+                  <a:t>Hz</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -6344,7 +6478,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR3.2 每圈片数</a:t>
+              <a:t>KR3.1 每面像素数</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -6386,12 +6520,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$141:$A$144</f>
+              <f>'指标趋势'!$A$141:$A$142</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$141:$B$144</f>
+              <f>'指标趋势'!$B$141:$B$142</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -6429,12 +6563,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$141:$A$144</f>
+              <f>'指标趋势'!$A$141:$A$142</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$141:$C$144</f>
+              <f>'指标趋势'!$C$141:$C$142</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -6555,7 +6689,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46308"/>
-          <min val="46231"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -6597,7 +6731,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>片</a:t>
+                  <a:t>px</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -7125,6 +7259,28 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>393</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="24" name="Chart 24"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId24"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -7471,7 +7627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7700,10 +7856,10 @@
         <v>100</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
@@ -7716,7 +7872,7 @@
         </is>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>1</v>
+        <v>0.7368421052631579</v>
       </c>
     </row>
     <row r="6">
@@ -7726,29 +7882,29 @@
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>KR1.3</t>
+          <t>KR1.7</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>WiFi 可用带宽</t>
+          <t>端到端延迟抖动 p99</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Mbit/s</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>越大越好</t>
+          <t>越小越好</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>160</v>
+        <v>236.6</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
@@ -7756,13 +7912,13 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -7771,11 +7927,11 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_m90_wifi_p2p_1012.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>1</v>
+        <v>0.5071851225697379</v>
       </c>
     </row>
     <row r="7">
@@ -7785,29 +7941,29 @@
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>KR1.4</t>
+          <t>KR1.3</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>主机出帧耗时 p99</t>
+          <t>WiFi 可用带宽</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>Mbit/s</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>越小越好</t>
+          <t>越大越好</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
@@ -7815,13 +7971,13 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
@@ -7830,7 +7986,7 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>claude_memory/project_m90_wifi_p2p_1012.md</t>
         </is>
       </c>
       <c r="Q7" s="8" t="n">
@@ -7844,12 +8000,12 @@
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>KR1.5</t>
+          <t>KR1.4</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>板上切片耗时 (每帧)</t>
+          <t>主机出帧耗时 p99</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -7863,7 +8019,7 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>17.3</v>
+        <v>22</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>46308</v>
@@ -7874,122 +8030,108 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 9bf16ad</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>KR1.5</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>板上切片耗时 (每帧)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>越小越好</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
+      <c r="P9" s="6" t="inlineStr">
         <is>
           <t>dr1v90 596b191</t>
         </is>
       </c>
-      <c r="Q8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="n"/>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="Q9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>KR1.6</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>内容刷新率 (实转上屏)</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>越大越好</t>
         </is>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>10.8</v>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>46307</v>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>V0 2047</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>claude_memory/project_slice_3bit_cpu_trial.md (D9 首次转起来 640–654 RPM)</t>
-        </is>
-      </c>
-      <c r="Q9" s="8" t="n">
-        <v>0.7200000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>体帧率达到 30 Hz</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>显示优化</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>✅ 达成当前期目标</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>KR2.1</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>体帧率</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>21.7</v>
       </c>
       <c r="J10" s="7" t="n">
         <v>46307</v>
@@ -8000,13 +8142,13 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>21.7</v>
+        <v>10.8</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
@@ -8015,20 +8157,20 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md (D9 首次转起来 640–654 RPM)</t>
         </is>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>0.7233333333333333</v>
+        <v>0.7200000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>画面更清晰</t>
+          <t>体帧率达到 30 Hz</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -8043,17 +8185,17 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>每面像素数</t>
+          <t>体帧率</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -8062,7 +8204,7 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>28800</v>
+        <v>21.7</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>46307</v>
@@ -8073,55 +8215,69 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>0.7233333333333333</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>画面更清晰</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>显示优化</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>KR3.1</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>每面像素数</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
         <v>28800</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>28800</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>41472</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>0.6944444444444444</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>KR3.2</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>每圈片数</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>片</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>142</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>46307</v>
@@ -8132,69 +8288,55 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
+        <v>28800</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>28800</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>41472</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>KR3.2</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>每圈片数</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>片</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
         <v>142</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>358</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>605</v>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>0.2347107438016529</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>颜色更丰富</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>显示优化</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>⏸ 无数据 / 未开始</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>KR4.1</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>色深</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>bit/通道</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>3</v>
       </c>
       <c r="J13" s="7" t="n">
         <v>46307</v>
@@ -8205,114 +8347,114 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>358</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>605</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>0.2347107438016529</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>颜色更丰富</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>显示优化</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>⏸ 无数据 / 未开始</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>KR4.1</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>色深</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>bit/通道</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="J14" s="7" t="n">
+        <v>46307</v>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
+      <c r="P14" s="6" t="inlineStr">
         <is>
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q13" s="8" t="n">
+      <c r="Q14" s="8" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>KR4.2</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>链路色深 12-bit 已验证 (1=是)</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>是/否</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>46308</v>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>仿真</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="11" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 cdf49c6 (gw5a_bridge/p1 verify ALL PASS)</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>立体像不变形、两面对齐、无重影</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>几何</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>🔄 进行中 / 未达标</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>KR5.1</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -8333,7 +8475,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="L15" s="3" t="n">
@@ -8345,14 +8487,14 @@
       <c r="N15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>⏸</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 cdf49c6 (gw5a_bridge/p1 verify ALL PASS)</t>
         </is>
       </c>
       <c r="Q15" s="8" t="n">
@@ -8360,18 +8502,32 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
+      <c r="A16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>立体像不变形、两面对齐、无重影</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>几何</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>🔄 进行中 / 未达标</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>KR5.1</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>左右镜像已核实 (1=已核)</t>
+          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -8385,7 +8541,7 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="7" t="n">
         <v>46308</v>
@@ -8404,64 +8560,50 @@
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O16" s="12" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
       <c r="Q16" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>左右镜像已核实 (1=已核)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>亮度合适、停转不伤眼</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>显示优化</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>✅ 达成当前期目标</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>KR6.1</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>停转自动低亮 (1=有)</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>是/否</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="J17" s="7" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
@@ -8477,64 +8619,64 @@
       <c r="N17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 3bc5736</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>长时间稳定</t>
+          <t>亮度合适、停转不伤眼</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>稳定</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>🔄 进行中 / 未达标</t>
+          <t>显示优化</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR6.1</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>停转自动低亮 (1=有)</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>越小越好</t>
+          <t>越大越好</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
@@ -8542,13 +8684,13 @@
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
@@ -8557,7 +8699,7 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 3bc5736</t>
         </is>
       </c>
       <c r="Q18" s="8" t="n">
@@ -8565,32 +8707,46 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
+      <c r="A19" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>稳定</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>🔄 进行中 / 未达标</t>
+        </is>
+      </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>连续无故障运行时长</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>越大越好</t>
+          <t>越小越好</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="J19" s="7" t="n">
         <v>46308</v>
@@ -8601,319 +8757,269 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 596b191</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M19" s="3" t="n">
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>KR7.2</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>连续无故障: 软件链路 (假转, 无人值守)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="M20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="O19" s="12" t="inlineStr">
+      <c r="O20" s="12" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr">
+      <c r="P20" s="6" t="inlineStr">
         <is>
           <t>dr1v90 596b191</t>
         </is>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="Q20" s="8" t="n">
         <v>0.007083333333333334</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>KR7.3</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>连续无故障: 整机实转 (有人值守)</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="6" t="inlineStr"/>
+      <c r="L21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr"/>
+      <c r="Q21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>上电即用</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>运维</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>✅ 达成当前期目标</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>🔄 进行中 / 未达标</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>KR8.1</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>上电到出图</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>上电到 0° 片亮起 (停转)</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>越小越好</t>
         </is>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" s="11" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr"/>
+      <c r="Q22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>KR8.4</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>上电到转稳全亮</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>越小越好</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J23" s="7" t="n">
         <v>46307</v>
       </c>
-      <c r="K20" s="6" t="inlineStr">
+      <c r="K23" s="6" t="inlineStr">
         <is>
           <t>V0 2047</t>
         </is>
       </c>
-      <c r="L20" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
         <is>
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q20" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="Q23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>KR8.2</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>按名字找到板子</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>越小越好</t>
         </is>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I24" s="3" t="n">
         <v>34</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>46308</v>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>V0 2047</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 b0f6b5d</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>KR8.3</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>需要串口 (1=需要)</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>是/否</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>越小越好</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>46307</v>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>V0 2047</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 30d82f9</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>转起来能看状态、能远程升级</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>运维</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>🔄 进行中 / 未达标</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>KR9.1</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>转子遥测可用 (1=可用)</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>是/否</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="7" t="n">
-        <v>46308</v>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>V0 2047</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="12" t="inlineStr">
-        <is>
-          <t>🔄</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>KR9.2</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>远程升级失败自动回滚 (1=有)</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>是/否</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>46308</v>
@@ -8924,128 +9030,128 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 b0f6b5d</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>KR8.3</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>需要串口 (1=需要)</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>越小越好</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>46307</v>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 30d82f9</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="M24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" s="12" t="inlineStr">
-        <is>
-          <t>🔄</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="n">
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>转起来能看状态、能远程升级</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>运维</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>🔄 进行中 / 未达标</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>KR9.1</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>转子遥测可用 (1=可用)</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>能放更多内容</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>✅ 达成当前期目标</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>KR10.1</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>可实时播放内容数</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="7" t="n">
-        <v>46308</v>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>V0 2047</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>dr1v90 887491a (live_push/README.md)</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>KR10.2</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>交互方式数</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>种</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>越大越好</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="J26" s="7" t="n">
         <v>46308</v>
@@ -9059,75 +9165,266 @@
         <v>1</v>
       </c>
       <c r="M26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/rotor-ops 05c4231</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>KR9.2</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>远程升级失败自动回滚 (1=有)</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/rotor-ops 05c4231</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>能放更多内容</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>KR10.1</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>可实时播放内容数</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="J28" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="M28" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="P26" s="6" t="inlineStr">
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 887491a (live_push/README.md)</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>KR10.2</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>交互方式数</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>种</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>越大越好</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
         <is>
           <t>dr1v90 live_push/README.md</t>
         </is>
       </c>
-      <c r="Q26" s="8" t="n">
+      <c r="Q29" s="8" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>达成当前期目标</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>进行中 / 未达标</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>无数据 / 未开始</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>退步 / 阻塞</t>
         </is>
@@ -9135,39 +9432,39 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D4:D10"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="C4:C10"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C14:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9179,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I380"/>
+  <dimension ref="A1:I397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9423,13 +9720,13 @@
         <v>46307</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H22" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
@@ -9443,19 +9740,19 @@
         <v>46309</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H23" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>KR1.3 WiFi 可用带宽 (Mbit/s, 越大越好)</t>
+          <t>KR1.7 端到端延迟抖动 p99 (ms, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -9508,89 +9805,55 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>46157</v>
+        <v>46308</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>2.02</v>
+        <v>236.6</v>
       </c>
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="19" t="n">
-        <v>46157</v>
+        <v>46307</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>46157</v>
+        <v>46307</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>46157</v>
+        <v>46307</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="19" t="n">
-        <v>46238</v>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="C40" s="3" t="n"/>
       <c r="D40" s="19" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="C41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="19" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>136</v>
-      </c>
-      <c r="C42" s="3" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="C43" s="3" t="n"/>
+        <v>120</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>KR1.4 主机出帧耗时 p99 (ms, 越小越好)</t>
+          <t>KR1.3 WiFi 可用带宽 (Mbit/s, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -9643,62 +9906,89 @@
     </row>
     <row r="56">
       <c r="A56" s="19" t="n">
-        <v>46307</v>
+        <v>46157</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>161</v>
+        <v>2.02</v>
       </c>
       <c r="C56" s="3" t="n"/>
       <c r="D56" s="19" t="n">
-        <v>46307</v>
+        <v>46157</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F56" s="19" t="n">
-        <v>46307</v>
+        <v>46157</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>46307</v>
+        <v>46157</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
-        <v>46308</v>
+        <v>46238</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="C57" s="3" t="n"/>
       <c r="D57" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F57" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>50</v>
-      </c>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="C58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="C59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="C60" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t>KR1.5 板上切片耗时 (每帧) (ms, 越小越好)</t>
+          <t>KR1.4 主机出帧耗时 p99 (ms, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -9726,6 +10016,26 @@
       <c r="E72" s="18" t="inlineStr">
         <is>
           <t>V0 目标</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标 日期</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标</t>
+        </is>
+      </c>
+      <c r="H72" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标 日期</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标</t>
         </is>
       </c>
     </row>
@@ -9734,14 +10044,26 @@
         <v>46307</v>
       </c>
       <c r="B73" s="3" t="n">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="C73" s="3" t="n"/>
       <c r="D73" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="F73" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H73" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="74">
@@ -9749,20 +10071,32 @@
         <v>46308</v>
       </c>
       <c r="B74" s="3" t="n">
-        <v>17.3</v>
+        <v>22</v>
       </c>
       <c r="C74" s="3" t="n"/>
       <c r="D74" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="F74" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H74" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>KR1.6 内容刷新率 (实转上屏) (fps, 越大越好)</t>
+          <t>KR1.5 板上切片耗时 (每帧) (ms, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -9790,26 +10124,6 @@
       <c r="E89" s="18" t="inlineStr">
         <is>
           <t>V0 目标</t>
-        </is>
-      </c>
-      <c r="F89" s="18" t="inlineStr">
-        <is>
-          <t>V1 目标 日期</t>
-        </is>
-      </c>
-      <c r="G89" s="18" t="inlineStr">
-        <is>
-          <t>V1 目标</t>
-        </is>
-      </c>
-      <c r="H89" s="18" t="inlineStr">
-        <is>
-          <t>V2 目标 日期</t>
-        </is>
-      </c>
-      <c r="I89" s="18" t="inlineStr">
-        <is>
-          <t>V2 目标</t>
         </is>
       </c>
     </row>
@@ -9818,52 +10132,35 @@
         <v>46307</v>
       </c>
       <c r="B90" s="3" t="n">
-        <v>10.8</v>
+        <v>35</v>
       </c>
       <c r="C90" s="3" t="n"/>
       <c r="D90" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F90" s="19" t="n">
-        <v>46306</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H90" s="19" t="n">
-        <v>46306</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91">
+      <c r="A91" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="C91" s="3" t="n"/>
       <c r="D91" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F91" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H91" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="17" t="inlineStr">
         <is>
-          <t>KR2.1 体帧率 (Hz, 越大越好)</t>
+          <t>KR1.6 内容刷新率 (实转上屏) (fps, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -9916,71 +10213,55 @@
     </row>
     <row r="107">
       <c r="A107" s="19" t="n">
-        <v>46238</v>
+        <v>46307</v>
       </c>
       <c r="B107" s="3" t="n">
-        <v>22.1</v>
+        <v>10.8</v>
       </c>
       <c r="C107" s="3" t="n"/>
       <c r="D107" s="19" t="n">
-        <v>46238</v>
+        <v>46306</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>21.7</v>
+        <v>10.8</v>
       </c>
       <c r="F107" s="19" t="n">
-        <v>46238</v>
+        <v>46306</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H107" s="19" t="n">
-        <v>46238</v>
+        <v>46306</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B108" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="C108" s="3" t="n"/>
       <c r="D108" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>21.7</v>
+        <v>10.8</v>
       </c>
       <c r="F108" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H108" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B109" s="3" t="n"/>
-      <c r="C109" s="3" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="17" t="inlineStr">
         <is>
-          <t>KR3.1 每面像素数 (px, 越大越好)</t>
+          <t>KR2.1 体帧率 (Hz, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10033,62 +10314,71 @@
     </row>
     <row r="124">
       <c r="A124" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="B124" s="3" t="n">
-        <v>28800</v>
+        <v>22.1</v>
       </c>
       <c r="C124" s="3" t="n"/>
       <c r="D124" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>28800</v>
+        <v>21.7</v>
       </c>
       <c r="F124" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>28800</v>
+        <v>24</v>
       </c>
       <c r="H124" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>41472</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B125" s="3" t="n"/>
-      <c r="C125" s="3" t="n">
-        <v>28800</v>
-      </c>
+        <v>46307</v>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="C125" s="3" t="n"/>
       <c r="D125" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>28800</v>
+        <v>21.7</v>
       </c>
       <c r="F125" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>28800</v>
+        <v>24</v>
       </c>
       <c r="H125" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>41472</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B126" s="3" t="n"/>
+      <c r="C126" s="3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="17" t="inlineStr">
         <is>
-          <t>KR3.2 每圈片数 (片, 越大越好)</t>
+          <t>KR3.1 每面像素数 (px, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10141,80 +10431,62 @@
     </row>
     <row r="141">
       <c r="A141" s="19" t="n">
-        <v>46231</v>
+        <v>46307</v>
       </c>
       <c r="B141" s="3" t="n">
-        <v>360</v>
+        <v>28800</v>
       </c>
       <c r="C141" s="3" t="n"/>
       <c r="D141" s="19" t="n">
-        <v>46231</v>
+        <v>46307</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>142</v>
+        <v>28800</v>
       </c>
       <c r="F141" s="19" t="n">
-        <v>46231</v>
+        <v>46307</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>358</v>
+        <v>28800</v>
       </c>
       <c r="H141" s="19" t="n">
-        <v>46231</v>
+        <v>46307</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>605</v>
+        <v>41472</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="19" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B142" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="C142" s="3" t="n"/>
+        <v>46308</v>
+      </c>
+      <c r="B142" s="3" t="n"/>
+      <c r="C142" s="3" t="n">
+        <v>28800</v>
+      </c>
       <c r="D142" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>142</v>
+        <v>28800</v>
       </c>
       <c r="F142" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>358</v>
+        <v>28800</v>
       </c>
       <c r="H142" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B143" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="C143" s="3" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B144" s="3" t="n"/>
-      <c r="C144" s="3" t="n">
-        <v>358</v>
+        <v>41472</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="17" t="inlineStr">
         <is>
-          <t>KR4.1 色深 (bit/通道, 越大越好)</t>
+          <t>KR3.2 每圈片数 (片, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10270,86 +10542,77 @@
         <v>46231</v>
       </c>
       <c r="B158" s="3" t="n">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="C158" s="3" t="n"/>
       <c r="D158" s="19" t="n">
         <v>46231</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="F158" s="19" t="n">
         <v>46231</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>12</v>
+        <v>358</v>
       </c>
       <c r="H158" s="19" t="n">
         <v>46231</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>12</v>
+        <v>605</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="19" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B159" s="3" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="C159" s="3" t="n"/>
       <c r="D159" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="F159" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>12</v>
+        <v>358</v>
       </c>
       <c r="H159" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>12</v>
+        <v>605</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="19" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B160" s="3" t="n"/>
-      <c r="C160" s="3" t="n">
-        <v>12</v>
-      </c>
+        <v>46307</v>
+      </c>
+      <c r="B160" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="C160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B161" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C161" s="3" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B162" s="3" t="n"/>
-      <c r="C162" s="3" t="n">
-        <v>12</v>
+      <c r="B161" s="3" t="n"/>
+      <c r="C161" s="3" t="n">
+        <v>358</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="17" t="inlineStr">
         <is>
-          <t>KR4.2 链路色深 12-bit 已验证 (1=是) (是/否, 越大越好)</t>
+          <t>KR4.1 色深 (bit/通道, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10402,55 +10665,89 @@
     </row>
     <row r="175">
       <c r="A175" s="19" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B175" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" s="3" t="n"/>
+      <c r="D175" s="19" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F175" s="19" t="n">
+        <v>46231</v>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H175" s="19" t="n">
+        <v>46231</v>
+      </c>
+      <c r="I175" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="19" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C176" s="3" t="n"/>
+      <c r="D176" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B175" s="3" t="n"/>
-      <c r="C175" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D175" s="19" t="n">
+      <c r="E176" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F176" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H176" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I176" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="19" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B177" s="3" t="n"/>
+      <c r="C177" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="E175" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F175" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="G175" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H175" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="I175" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="D176" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F176" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="G176" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H176" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I176" s="3" t="n">
-        <v>1</v>
+      <c r="B178" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C178" s="3" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B179" s="3" t="n"/>
+      <c r="C179" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="17" t="inlineStr">
         <is>
-          <t>KR5.1 几何 LUT 复现正确 (1=逐字节复现) (是/否, 越大越好)</t>
+          <t>KR4.2 链路色深 12-bit 已验证 (1=是) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10503,53 +10800,46 @@
     </row>
     <row r="192">
       <c r="A192" s="19" t="n">
-        <v>46238</v>
-      </c>
-      <c r="B192" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B192" s="3" t="n"/>
+      <c r="C192" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C192" s="3" t="n"/>
       <c r="D192" s="19" t="n">
-        <v>46238</v>
+        <v>46307</v>
       </c>
       <c r="E192" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F192" s="19" t="n">
-        <v>46238</v>
+        <v>46307</v>
       </c>
       <c r="G192" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H192" s="19" t="n">
-        <v>46238</v>
+        <v>46307</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B193" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C193" s="3" t="n"/>
       <c r="D193" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E193" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F193" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G193" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H193" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I193" s="3" t="n">
         <v>1</v>
@@ -10558,7 +10848,7 @@
     <row r="207">
       <c r="A207" s="17" t="inlineStr">
         <is>
-          <t>KR5.2 左右镜像已核实 (1=已核) (是/否, 越大越好)</t>
+          <t>KR5.1 几何 LUT 复现正确 (1=逐字节复现) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10611,46 +10901,53 @@
     </row>
     <row r="209">
       <c r="A209" s="19" t="n">
-        <v>46308</v>
+        <v>46238</v>
       </c>
       <c r="B209" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C209" s="3" t="n"/>
       <c r="D209" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="E209" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F209" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="G209" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H209" s="19" t="n">
-        <v>46307</v>
+        <v>46238</v>
       </c>
       <c r="I209" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="210">
+      <c r="A210" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B210" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" s="3" t="n"/>
       <c r="D210" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E210" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F210" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G210" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H210" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>1</v>
@@ -10659,7 +10956,7 @@
     <row r="224">
       <c r="A224" s="17" t="inlineStr">
         <is>
-          <t>KR6.1 停转自动低亮 (1=有) (是/否, 越大越好)</t>
+          <t>KR5.2 左右镜像已核实 (1=已核) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10712,26 +11009,26 @@
     </row>
     <row r="226">
       <c r="A226" s="19" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B226" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C226" s="3" t="n"/>
       <c r="D226" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E226" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F226" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="G226" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H226" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I226" s="3" t="n">
         <v>1</v>
@@ -10739,19 +11036,19 @@
     </row>
     <row r="227">
       <c r="D227" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E227" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F227" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G227" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H227" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I227" s="3" t="n">
         <v>1</v>
@@ -10760,7 +11057,7 @@
     <row r="241">
       <c r="A241" s="17" t="inlineStr">
         <is>
-          <t>KR7.1 丢帧/迟到率 (%, 越小越好)</t>
+          <t>KR6.1 停转自动低亮 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -10813,57 +11110,55 @@
     </row>
     <row r="243">
       <c r="A243" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B243" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C243" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C243" s="3" t="n"/>
       <c r="D243" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="E243" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F243" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H243" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="I243" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="D244" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E244" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F244" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H244" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="17" t="inlineStr">
         <is>
-          <t>KR7.2 连续无故障运行时长 (h, 越大越好)</t>
+          <t>KR7.1 丢帧/迟到率 (%, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -10916,62 +11211,57 @@
     </row>
     <row r="260">
       <c r="A260" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B260" s="3" t="n"/>
+        <v>46308</v>
+      </c>
+      <c r="B260" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C260" s="3" t="n">
-        <v>47.9</v>
+        <v>0</v>
       </c>
       <c r="D260" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E260" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F260" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>8</v>
+        <v>0.1</v>
       </c>
       <c r="H260" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I260" s="3" t="n">
-        <v>24</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B261" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="C261" s="3" t="n"/>
       <c r="D261" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E261" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F261" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>8</v>
+        <v>0.1</v>
       </c>
       <c r="H261" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>24</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="17" t="inlineStr">
         <is>
-          <t>KR8.1 上电到出图 (s, 越小越好)</t>
+          <t>KR7.2 连续无故障: 软件链路 (假转, 无人值守) (h, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -11026,53 +11316,60 @@
       <c r="A277" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="B277" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="C277" s="3" t="n"/>
+      <c r="B277" s="3" t="n"/>
+      <c r="C277" s="3" t="n">
+        <v>47.9</v>
+      </c>
       <c r="D277" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E277" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F277" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="G277" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H277" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I277" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="278">
+      <c r="A278" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B278" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C278" s="3" t="n"/>
       <c r="D278" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="E278" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F278" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="G278" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H278" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="I278" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="17" t="inlineStr">
         <is>
-          <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
+          <t>KR8.4 上电到转稳全亮 (s, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -11092,88 +11389,20 @@
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D293" s="18" t="inlineStr">
-        <is>
-          <t>V0 目标 日期</t>
-        </is>
-      </c>
-      <c r="E293" s="18" t="inlineStr">
-        <is>
-          <t>V0 目标</t>
-        </is>
-      </c>
-      <c r="F293" s="18" t="inlineStr">
-        <is>
-          <t>V1 目标 日期</t>
-        </is>
-      </c>
-      <c r="G293" s="18" t="inlineStr">
-        <is>
-          <t>V1 目标</t>
-        </is>
-      </c>
-      <c r="H293" s="18" t="inlineStr">
-        <is>
-          <t>V2 目标 日期</t>
-        </is>
-      </c>
-      <c r="I293" s="18" t="inlineStr">
-        <is>
-          <t>V2 目标</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B294" s="3" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C294" s="3" t="n"/>
-      <c r="D294" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="E294" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F294" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="G294" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H294" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="I294" s="3" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="D295" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="E295" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F295" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="G295" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H295" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I295" s="3" t="n">
-        <v>60</v>
-      </c>
     </row>
     <row r="309">
       <c r="A309" s="17" t="inlineStr">
         <is>
-          <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
+          <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -11226,55 +11455,55 @@
     </row>
     <row r="311">
       <c r="A311" s="19" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B311" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C311" s="3" t="n"/>
       <c r="D311" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E311" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F311" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="G311" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H311" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I311" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="312">
       <c r="D312" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E312" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F312" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G312" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H312" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I312" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="17" t="inlineStr">
         <is>
-          <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
+          <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -11327,55 +11556,55 @@
     </row>
     <row r="328">
       <c r="A328" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B328" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C328" s="3" t="n"/>
       <c r="D328" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="E328" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F328" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H328" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="I328" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c r="D329" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E329" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F329" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H329" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I329" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="17" t="inlineStr">
         <is>
-          <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
+          <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11705,7 @@
     <row r="360">
       <c r="A360" s="17" t="inlineStr">
         <is>
-          <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
+          <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -11532,26 +11761,26 @@
         <v>46308</v>
       </c>
       <c r="B362" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C362" s="3" t="n"/>
       <c r="D362" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E362" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F362" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="G362" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H362" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I362" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363">
@@ -11559,25 +11788,25 @@
         <v>46309</v>
       </c>
       <c r="E363" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F363" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="G363" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H363" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="I363" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="17" t="inlineStr">
         <is>
-          <t>KR10.2 交互方式数 (种, 越大越好)</t>
+          <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -11633,26 +11862,26 @@
         <v>46308</v>
       </c>
       <c r="B379" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C379" s="3" t="n"/>
       <c r="D379" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E379" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F379" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="G379" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H379" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I379" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="380">
@@ -11660,18 +11889,119 @@
         <v>46309</v>
       </c>
       <c r="E380" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F380" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="G380" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H380" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="I380" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="17" t="inlineStr">
+        <is>
+          <t>KR10.2 交互方式数 (种, 越大越好)</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="18" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B395" s="18" t="inlineStr">
+        <is>
+          <t>实测</t>
+        </is>
+      </c>
+      <c r="C395" s="18" t="inlineStr">
+        <is>
+          <t>仿真/台架</t>
+        </is>
+      </c>
+      <c r="D395" s="18" t="inlineStr">
+        <is>
+          <t>V0 目标 日期</t>
+        </is>
+      </c>
+      <c r="E395" s="18" t="inlineStr">
+        <is>
+          <t>V0 目标</t>
+        </is>
+      </c>
+      <c r="F395" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标 日期</t>
+        </is>
+      </c>
+      <c r="G395" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标</t>
+        </is>
+      </c>
+      <c r="H395" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标 日期</t>
+        </is>
+      </c>
+      <c r="I395" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B396" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C396" s="3" t="n"/>
+      <c r="D396" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E396" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F396" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G396" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H396" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="I396" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="D397" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E397" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F397" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G397" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H397" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I397" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12769,7 +13099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -14033,7 +14363,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>连续无故障运行时长</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守)</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -14069,21 +14399,21 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>KR8.1</t>
+          <t>KR8.3</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>上电到出图</t>
+          <t>需要串口 (1=需要)</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
@@ -14092,12 +14422,12 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
+          <t>dr1v90 30d82f9</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>重启后 uptime 26 s 转速门控亮起播 walking</t>
+          <t>开机自连 WiFi 重启实测通过，用户拔掉串口</t>
         </is>
       </c>
     </row>
@@ -14110,21 +14440,21 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>KR8.3</t>
+          <t>KR8.4</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>需要串口 (1=需要)</t>
+          <t>上电到转稳全亮</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>s</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
@@ -14133,12 +14463,12 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 30d82f9</t>
+          <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>开机自连 WiFi 重启实测通过，用户拔掉串口</t>
+          <t>重启后 uptime 26 s 转速门控亮起播 walking</t>
         </is>
       </c>
     </row>
@@ -14475,25 +14805,25 @@
         <v>46308</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>KR10.1</t>
+          <t>KR1.7</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>可实时播放内容数</t>
+          <t>端到端延迟抖动 p99</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
@@ -14502,12 +14832,12 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 887491a (live_push/README.md)</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>walking / groot 实时推流逐字节核过</t>
+          <t>agent 上板实测 p99</t>
         </is>
       </c>
     </row>
@@ -14516,25 +14846,25 @@
         <v>46308</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>KR10.2</t>
+          <t>KR1.7</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>交互方式数</t>
+          <t>端到端延迟抖动 p99</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>种</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1</v>
+        <v>236.6</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
@@ -14543,12 +14873,12 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 live_push/README.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>--keys 键盘旋转/缩放</t>
+          <t>主会话新克隆独立复验 p99 (9381 帧)</t>
         </is>
       </c>
     </row>
@@ -14557,39 +14887,39 @@
         <v>46308</v>
       </c>
       <c r="B44" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>KR10.1</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>可实时播放内容数</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>KR2.1</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>体帧率</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>30</v>
-      </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f</t>
+          <t>dr1v90 887491a (live_push/README.md)</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>30 Hz 纯切片位流第一次上硅 (无屏)：切片链按 30 Hz 节拍跑通，尾部 late 0.2%</t>
+          <t>walking / groot 实时推流逐字节核过</t>
         </is>
       </c>
     </row>
@@ -14598,39 +14928,39 @@
         <v>46308</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>KR2.1</t>
+          <t>KR10.2</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>体帧率</t>
+          <t>交互方式数</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>种</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>仿真</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 live_push/README.md</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>1 期桥 6 链 1串2 4296 片/s = 24 Hz×358 片 (余量 0.40%)</t>
+          <t>--keys 键盘旋转/缩放</t>
         </is>
       </c>
     </row>
@@ -14639,39 +14969,39 @@
         <v>46308</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>每面像素数</t>
+          <t>体帧率</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>28800</v>
+        <v>30</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>仿真</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 71d006f</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>1 期 2260 验证板 160×180</t>
+          <t>30 Hz 纯切片位流第一次上硅 (无屏)：切片链按 30 Hz 节拍跑通，尾部 late 0.2%</t>
         </is>
       </c>
     </row>
@@ -14680,25 +15010,25 @@
         <v>46308</v>
       </c>
       <c r="B47" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>KR3.2</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>每圈片数</t>
+          <t>体帧率</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>片</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>358</v>
+        <v>24</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
@@ -14707,12 +15037,12 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 a9fc48c / cdf49c6</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>1 期 LUT 358 片 + 桥仿真</t>
+          <t>1 期桥 6 链 1串2 4296 片/s = 24 Hz×358 片 (余量 0.40%)</t>
         </is>
       </c>
     </row>
@@ -14721,25 +15051,25 @@
         <v>46308</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>KR4.1</t>
+          <t>KR3.1</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>色深</t>
+          <t>每面像素数</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>bit/通道</t>
+          <t>px</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>12</v>
+        <v>28800</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
@@ -14753,7 +15083,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>1 期桥 12-bit 整链仿真 PASS</t>
+          <t>1 期 2260 验证板 160×180</t>
         </is>
       </c>
     </row>
@@ -14762,25 +15092,25 @@
         <v>46308</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>KR4.2</t>
+          <t>KR3.2</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>链路色深 12-bit 已验证 (1=是)</t>
+          <t>每圈片数</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>片</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
@@ -14789,12 +15119,12 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6 (gw5a_bridge/p1 verify ALL PASS)</t>
+          <t>dr1v90 a9fc48c / cdf49c6</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>仅桥→2260 段仿真; 主控→桥→2260 全链未验</t>
+          <t>1 期 LUT 358 片 + 桥仿真</t>
         </is>
       </c>
     </row>
@@ -14803,39 +15133,39 @@
         <v>46308</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>KR5.1</t>
+          <t>KR4.1</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
+          <t>色深</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>bit/通道</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
+          <t>1 期桥 12-bit 整链仿真 PASS</t>
         </is>
       </c>
     </row>
@@ -14844,16 +15174,16 @@
         <v>46308</v>
       </c>
       <c r="B51" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>左右镜像已核实 (1=已核)</t>
+          <t>链路色深 12-bit 已验证 (1=是)</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -14862,21 +15192,21 @@
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6 (gw5a_bridge/p1 verify ALL PASS)</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>2047 是否整体左右镜像未核</t>
+          <t>仅桥→2260 段仿真; 主控→桥→2260 全链未验</t>
         </is>
       </c>
     </row>
@@ -14885,39 +15215,39 @@
         <v>46308</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR5.1</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
         </is>
       </c>
     </row>
@@ -14926,21 +15256,21 @@
         <v>46308</v>
       </c>
       <c r="B53" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>左右镜像已核实 (1=已核)</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
@@ -14948,17 +15278,17 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 473abcf</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
+          <t>2047 是否整体左右镜像未核</t>
         </is>
       </c>
     </row>
@@ -14985,21 +15315,21 @@
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>实时推流 624 s NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
         </is>
       </c>
     </row>
@@ -15012,35 +15342,35 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>连续无故障运行时长</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 473abcf</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>实时推流连续 624 s 无故障 (未做更长)</t>
+          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
         </is>
       </c>
     </row>
@@ -15049,25 +15379,25 @@
         <v>46308</v>
       </c>
       <c r="B56" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>按名字找到板子</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
@@ -15076,12 +15406,12 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>实时推流 624 s NAK 0 / forced 0</t>
         </is>
       </c>
     </row>
@@ -15090,25 +15420,25 @@
         <v>46308</v>
       </c>
       <c r="B57" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用)</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守)</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -15117,12 +15447,12 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+          <t>实时推流连续 624 s 无故障 (未做更长)</t>
         </is>
       </c>
     </row>
@@ -15131,44 +15461,126 @@
         <v>46308</v>
       </c>
       <c r="B58" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>KR8.2</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>按名字找到板子</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 b0f6b5d</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B59" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>KR9.1</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>转子遥测可用 (1=可用)</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/rotor-ops 05c4231</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>KR9.2</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>远程升级失败自动回滚 (1=有)</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>是/否</t>
         </is>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="F60" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>V0 2047</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>dr1v90 task/rotor-ops 05c4231</t>
         </is>
       </c>
-      <c r="I58" s="6" t="inlineStr">
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>D7 返工中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I58"/>
+  <autoFilter ref="A1:I60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -12017,7 +12017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12061,7 +12061,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
@@ -12075,7 +12075,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>7</v>
@@ -12089,7 +12089,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>8</v>
@@ -12101,10 +12101,10 @@
         <v>46310</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="3" t="n"/>
     </row>
@@ -12113,10 +12113,10 @@
         <v>46311</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8" s="3" t="n"/>
     </row>
@@ -12125,10 +12125,10 @@
         <v>46312</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D9" s="3" t="n"/>
     </row>
@@ -12137,10 +12137,10 @@
         <v>46313</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="n"/>
     </row>
@@ -12149,10 +12149,10 @@
         <v>46314</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D11" s="3" t="n"/>
     </row>
@@ -12161,10 +12161,10 @@
         <v>46315</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D12" s="3" t="n"/>
     </row>
@@ -12173,10 +12173,10 @@
         <v>46316</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D13" s="3" t="n"/>
     </row>
@@ -12185,10 +12185,10 @@
         <v>46317</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D14" s="3" t="n"/>
     </row>
@@ -12197,10 +12197,10 @@
         <v>46318</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D15" s="3" t="n"/>
     </row>
@@ -12209,10 +12209,10 @@
         <v>46319</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D16" s="3" t="n"/>
     </row>
@@ -12936,17 +12936,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>启动阶段屏显 (停转 0° 片当平面屏: ①PL 静态 logo ②启动状态逐行显示, 走公共片流 ③转稳切正常内容)</t>
+          <t>延迟降低 (相位对齐) + 帧率跟转速</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>8;9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -12954,16 +12954,90 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E43" s="7" t="n"/>
+      <c r="E43" s="7" t="n">
+        <v>46310</v>
+      </c>
       <c r="F43" s="7" t="n"/>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>⏸ backlog 未派</t>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>用户 10-13 定只记录; 与 D7 最近</t>
+          <t>task/d12-latency</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>启动提速 + 启动屏显 (含原 backlog B1)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>task/d13-boot</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>更多内容 + 手机网页控制</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>task/d14-content</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -14,7 +14,7 @@
     <sheet name="历史记录" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4053,6 +4053,49 @@
           <order val="1"/>
           <tx>
             <strRef>
+              <f>'指标趋势'!C378</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="triangle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$379</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$C$379</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
               <f>'指标趋势'!E378</f>
             </strRef>
           </tx>
@@ -4085,8 +4128,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G378</f>
@@ -4121,8 +4164,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I378</f>
@@ -4295,6 +4338,49 @@
           <order val="1"/>
           <tx>
             <strRef>
+              <f>'指标趋势'!C395</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="triangle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$396</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$C$396</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
               <f>'指标趋势'!E395</f>
             </strRef>
           </tx>
@@ -4327,8 +4413,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G395</f>
@@ -4363,8 +4449,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I395</f>
@@ -11864,7 +11950,9 @@
       <c r="B379" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C379" s="3" t="n"/>
+      <c r="C379" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="D379" s="19" t="n">
         <v>46307</v>
       </c>
@@ -11965,7 +12053,9 @@
       <c r="B396" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C396" s="3" t="n"/>
+      <c r="C396" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="D396" s="19" t="n">
         <v>46307</v>
       </c>
@@ -12081,7 +12171,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -12665,15 +12755,17 @@
       <c r="E35" s="7" t="n">
         <v>46311</v>
       </c>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="F35" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>task/bridge-c1 (7a1a17f)</t>
+          <t>合主线 6a373d3</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15006,35 +15098,35 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>KR10.2</t>
+          <t>KR10.1</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>交互方式数</t>
+          <t>可实时播放内容数</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>种</t>
+          <t>个</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 live_push/README.md</t>
+          <t>dr1v90 ffbfeeb (live_content/verify.sh, 主会话复验)</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>--keys 键盘旋转/缩放</t>
+          <t>D14 离线: 10 类内容可实时出帧, 未上板</t>
         </is>
       </c>
     </row>
@@ -15043,39 +15135,39 @@
         <v>46308</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>KR2.1</t>
+          <t>KR10.2</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>体帧率</t>
+          <t>交互方式数</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>种</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f</t>
+          <t>dr1v90 live_push/README.md</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>30 Hz 纯切片位流第一次上硅 (无屏)：切片链按 30 Hz 节拍跑通，尾部 late 0.2%</t>
+          <t>--keys 键盘旋转/缩放</t>
         </is>
       </c>
     </row>
@@ -15084,26 +15176,26 @@
         <v>46308</v>
       </c>
       <c r="B47" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>KR10.2</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>交互方式数</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>种</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>KR2.1</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>体帧率</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>24</v>
-      </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
           <t>仿真</t>
@@ -15111,12 +15203,12 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>1 期桥 6 链 1串2 4296 片/s = 24 Hz×358 片 (余量 0.40%)</t>
+          <t>D14 手机网页遥控, 脚本模拟 24 项过, 未用真手机</t>
         </is>
       </c>
     </row>
@@ -15125,39 +15217,39 @@
         <v>46308</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>每面像素数</t>
+          <t>体帧率</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>28800</v>
+        <v>30</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>仿真</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 71d006f</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>1 期 2260 验证板 160×180</t>
+          <t>30 Hz 纯切片位流第一次上硅 (无屏)：切片链按 30 Hz 节拍跑通，尾部 late 0.2%</t>
         </is>
       </c>
     </row>
@@ -15166,25 +15258,25 @@
         <v>46308</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>KR3.2</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>每圈片数</t>
+          <t>体帧率</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>片</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>358</v>
+        <v>24</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
@@ -15193,12 +15285,12 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 a9fc48c / cdf49c6</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>1 期 LUT 358 片 + 桥仿真</t>
+          <t>1 期桥 6 链 1串2 4296 片/s = 24 Hz×358 片 (余量 0.40%)</t>
         </is>
       </c>
     </row>
@@ -15207,25 +15299,25 @@
         <v>46308</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>KR4.1</t>
+          <t>KR3.1</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>色深</t>
+          <t>每面像素数</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>bit/通道</t>
+          <t>px</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>12</v>
+        <v>28800</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
@@ -15239,7 +15331,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>1 期桥 12-bit 整链仿真 PASS</t>
+          <t>1 期 2260 验证板 160×180</t>
         </is>
       </c>
     </row>
@@ -15248,25 +15340,25 @@
         <v>46308</v>
       </c>
       <c r="B51" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>KR4.2</t>
+          <t>KR3.2</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>链路色深 12-bit 已验证 (1=是)</t>
+          <t>每圈片数</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>片</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
@@ -15275,12 +15367,12 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6 (gw5a_bridge/p1 verify ALL PASS)</t>
+          <t>dr1v90 a9fc48c / cdf49c6</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>仅桥→2260 段仿真; 主控→桥→2260 全链未验</t>
+          <t>1 期 LUT 358 片 + 桥仿真</t>
         </is>
       </c>
     </row>
@@ -15289,39 +15381,39 @@
         <v>46308</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>KR5.1</t>
+          <t>KR4.1</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
+          <t>色深</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>bit/通道</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
+          <t>1 期桥 12-bit 整链仿真 PASS</t>
         </is>
       </c>
     </row>
@@ -15330,16 +15422,16 @@
         <v>46308</v>
       </c>
       <c r="B53" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>左右镜像已核实 (1=已核)</t>
+          <t>链路色深 12-bit 已验证 (1=是)</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -15348,21 +15440,21 @@
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6 (gw5a_bridge/p1 verify ALL PASS)</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>2047 是否整体左右镜像未核</t>
+          <t>仅桥→2260 段仿真; 主控→桥→2260 全链未验</t>
         </is>
       </c>
     </row>
@@ -15371,39 +15463,39 @@
         <v>46308</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR5.1</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
         </is>
       </c>
     </row>
@@ -15412,21 +15504,21 @@
         <v>46308</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>左右镜像已核实 (1=已核)</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -15434,17 +15526,17 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 473abcf</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
+          <t>2047 是否整体左右镜像未核</t>
         </is>
       </c>
     </row>
@@ -15471,21 +15563,21 @@
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>实时推流 624 s NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
         </is>
       </c>
     </row>
@@ -15498,35 +15590,35 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>连续无故障: 软件链路 (假转, 无人值守)</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 473abcf</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>实时推流连续 624 s 无故障 (未做更长)</t>
+          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
         </is>
       </c>
     </row>
@@ -15535,25 +15627,25 @@
         <v>46308</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>按名字找到板子</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
@@ -15562,12 +15654,12 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>实时推流 624 s NAK 0 / forced 0</t>
         </is>
       </c>
     </row>
@@ -15576,25 +15668,25 @@
         <v>46308</v>
       </c>
       <c r="B59" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用)</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守)</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
@@ -15603,12 +15695,12 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+          <t>实时推流连续 624 s 无故障 (未做更长)</t>
         </is>
       </c>
     </row>
@@ -15617,44 +15709,126 @@
         <v>46308</v>
       </c>
       <c r="B60" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>KR8.2</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>按名字找到板子</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 b0f6b5d</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B61" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>KR9.1</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>转子遥测可用 (1=可用)</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/rotor-ops 05c4231</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>KR9.2</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>远程升级失败自动回滚 (1=有)</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E62" s="6" t="inlineStr">
         <is>
           <t>是/否</t>
         </is>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F62" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>V0 2047</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>dr1v90 task/rotor-ops 05c4231</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>D7 返工中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I60"/>
+  <autoFilter ref="A1:I62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -14,7 +14,7 @@
     <sheet name="历史记录" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8601,9 +8601,9 @@
           <t>几何</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>🔄 进行中 / 未达标</t>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="7" t="n">
         <v>46308</v>
@@ -8705,18 +8705,18 @@
       <c r="N17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O17" s="12" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6 (VOXSLICE_M90.md 10-13 节)</t>
         </is>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>46308</v>
@@ -9395,11 +9395,11 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 887491a (live_push/README.md)</t>
+          <t>dr1v90 task/d14-content ffbfeeb + 用户实转观看</t>
         </is>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -11098,7 +11098,7 @@
         <v>46308</v>
       </c>
       <c r="B226" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C226" s="3" t="n"/>
       <c r="D226" s="19" t="n">
@@ -11948,7 +11948,7 @@
         <v>46308</v>
       </c>
       <c r="B379" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C379" s="3" t="n">
         <v>10</v>
@@ -13265,7 +13265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15139,21 +15139,21 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>KR10.2</t>
+          <t>KR10.1</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>交互方式数</t>
+          <t>可实时播放内容数</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>种</t>
+          <t>个</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 live_push/README.md</t>
+          <t>dr1v90 task/d14-content ffbfeeb + 用户实转观看</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>--keys 键盘旋转/缩放</t>
+          <t>10 类内容实转轮播 + 手机遥控用户已看 (未跑正式上板验收)</t>
         </is>
       </c>
     </row>
@@ -15194,21 +15194,21 @@
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>仿真</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>dr1v90 live_push/README.md</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>D14 手机网页遥控, 脚本模拟 24 项过, 未用真手机</t>
+          <t>--keys 键盘旋转/缩放</t>
         </is>
       </c>
     </row>
@@ -15217,39 +15217,39 @@
         <v>46308</v>
       </c>
       <c r="B48" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>KR10.2</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>交互方式数</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>种</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>KR2.1</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>体帧率</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>30</v>
-      </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>30 Hz 纯切片位流第一次上硅 (无屏)：切片链按 30 Hz 节拍跑通，尾部 late 0.2%</t>
+          <t>D14 手机网页遥控, 脚本模拟 24 项过, 未用真手机</t>
         </is>
       </c>
     </row>
@@ -15276,21 +15276,21 @@
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>仿真</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 71d006f</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>1 期桥 6 链 1串2 4296 片/s = 24 Hz×358 片 (余量 0.40%)</t>
+          <t>30 Hz 纯切片位流第一次上硅 (无屏)：切片链按 30 Hz 节拍跑通，尾部 late 0.2%</t>
         </is>
       </c>
     </row>
@@ -15299,25 +15299,25 @@
         <v>46308</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>KR3.1</t>
+          <t>KR2.1</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>每面像素数</t>
+          <t>体帧率</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>28800</v>
+        <v>24</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>1 期 2260 验证板 160×180</t>
+          <t>1 期桥 6 链 1串2 4296 片/s = 24 Hz×358 片 (余量 0.40%)</t>
         </is>
       </c>
     </row>
@@ -15344,21 +15344,21 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>KR3.2</t>
+          <t>KR3.1</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>每圈片数</t>
+          <t>每面像素数</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>片</t>
+          <t>px</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>358</v>
+        <v>28800</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
@@ -15367,12 +15367,12 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 a9fc48c / cdf49c6</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>1 期 LUT 358 片 + 桥仿真</t>
+          <t>1 期 2260 验证板 160×180</t>
         </is>
       </c>
     </row>
@@ -15381,25 +15381,25 @@
         <v>46308</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>KR4.1</t>
+          <t>KR3.2</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>色深</t>
+          <t>每圈片数</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>bit/通道</t>
+          <t>片</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>12</v>
+        <v>358</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
@@ -15408,12 +15408,12 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 a9fc48c / cdf49c6</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>1 期桥 12-bit 整链仿真 PASS</t>
+          <t>1 期 LUT 358 片 + 桥仿真</t>
         </is>
       </c>
     </row>
@@ -15426,21 +15426,21 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>KR4.2</t>
+          <t>KR4.1</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>链路色深 12-bit 已验证 (1=是)</t>
+          <t>色深</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>bit/通道</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
@@ -15449,12 +15449,12 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6 (gw5a_bridge/p1 verify ALL PASS)</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>仅桥→2260 段仿真; 主控→桥→2260 全链未验</t>
+          <t>1 期桥 12-bit 整链仿真 PASS</t>
         </is>
       </c>
     </row>
@@ -15463,16 +15463,16 @@
         <v>46308</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>KR5.1</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
+          <t>链路色深 12-bit 已验证 (1=是)</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -15485,17 +15485,17 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 cdf49c6 (gw5a_bridge/p1 verify ALL PASS)</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
+          <t>仅桥→2260 段仿真; 主控→桥→2260 全链未验</t>
         </is>
       </c>
     </row>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>KR5.1</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>左右镜像已核实 (1=已核)</t>
+          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
@@ -15531,12 +15531,12 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>2047 是否整体左右镜像未核</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
         </is>
       </c>
     </row>
@@ -15545,39 +15545,39 @@
         <v>46308</v>
       </c>
       <c r="B56" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>左右镜像已核实 (1=已核)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
+          <t>2047 是否整体左右镜像未核</t>
         </is>
       </c>
     </row>
@@ -15586,39 +15586,39 @@
         <v>46308</v>
       </c>
       <c r="B57" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>左右镜像已核实 (1=已核)</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 473abcf</t>
+          <t>dr1v90 49031f6 (VOXSLICE_M90.md 10-13 节)</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
+          <t>用户实转核实: 旧表镜像, 已更正为 0decad54</t>
         </is>
       </c>
     </row>
@@ -15645,21 +15645,21 @@
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>实时推流 624 s NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
         </is>
       </c>
     </row>
@@ -15672,35 +15672,35 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>连续无故障: 软件链路 (假转, 无人值守)</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 473abcf</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>实时推流连续 624 s 无故障 (未做更长)</t>
+          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
         </is>
       </c>
     </row>
@@ -15709,25 +15709,25 @@
         <v>46308</v>
       </c>
       <c r="B60" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>按名字找到板子</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>实时推流 624 s NAK 0 / forced 0</t>
         </is>
       </c>
     </row>
@@ -15750,25 +15750,25 @@
         <v>46308</v>
       </c>
       <c r="B61" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用)</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守)</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
@@ -15777,12 +15777,12 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+          <t>实时推流连续 624 s 无故障 (未做更长)</t>
         </is>
       </c>
     </row>
@@ -15791,44 +15791,126 @@
         <v>46308</v>
       </c>
       <c r="B62" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>KR8.2</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>按名字找到板子</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 b0f6b5d</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>KR9.1</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>转子遥测可用 (1=可用)</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/rotor-ops 05c4231</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>KR9.2</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>远程升级失败自动回滚 (1=有)</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>是/否</t>
         </is>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="F64" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>V0 2047</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>dr1v90 task/rotor-ops 05c4231</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>D7 返工中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I62"/>
+  <autoFilter ref="A1:I64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -12107,7 +12107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12151,7 +12151,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
@@ -12165,7 +12165,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>7</v>
@@ -12179,7 +12179,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>8</v>
@@ -12191,7 +12191,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>10</v>
@@ -12203,7 +12203,7 @@
         <v>46311</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>15</v>
@@ -12215,10 +12215,10 @@
         <v>46312</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3" t="n"/>
     </row>
@@ -12227,10 +12227,10 @@
         <v>46313</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="n"/>
     </row>
@@ -12239,10 +12239,10 @@
         <v>46314</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3" t="n"/>
     </row>
@@ -12251,10 +12251,10 @@
         <v>46315</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="n"/>
     </row>
@@ -12263,10 +12263,10 @@
         <v>46316</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" s="3" t="n"/>
     </row>
@@ -12275,10 +12275,10 @@
         <v>46317</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" s="3" t="n"/>
     </row>
@@ -12287,10 +12287,10 @@
         <v>46318</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" s="3" t="n"/>
     </row>
@@ -12299,10 +12299,10 @@
         <v>46319</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" s="3" t="n"/>
     </row>
@@ -13130,6 +13130,78 @@
       <c r="H45" s="6" t="inlineStr">
         <is>
           <t>task/d14-content</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>WiFi 端 12-bit 色深通路 (像素位宽 16/32 可配)</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>task/d15-color</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>16 bit DDR 做到极限 (A 线: 慢读定位/分端口/预取缓冲/兜底)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>7;2</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>task/d16-ddr</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -9012,13 +9012,13 @@
       <c r="J22" s="7" t="n"/>
       <c r="K22" s="6" t="inlineStr"/>
       <c r="L22" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>

--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -14,7 +14,7 @@
     <sheet name="历史记录" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'历史记录'!$A$1:$I$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2652,7 +2652,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.4 上电到转稳全亮</a:t>
+              <a:t>KR8.1 上电到 0° 片亮起 (停转)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2704,6 +2704,114 @@
           </yVal>
           <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!E293</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$D$294:$D$295</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$E$294:$E$295</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!G293</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$F$294:$F$295</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$G$294:$G$295</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!I293</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$H$294:$H$295</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$I$294:$I$295</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -2711,8 +2819,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
-          <min val="46306"/>
+          <max val="46309"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2786,7 +2894,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.2 按名字找到板子</a:t>
+              <a:t>KR8.4 上电到转稳全亮</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2838,114 +2946,6 @@
           </yVal>
           <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!E310</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="70AD47"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$D$311:$D$312</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$E$311:$E$312</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!G310</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$F$311:$F$312</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$G$311:$G$312</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'指标趋势'!I310</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$H$311:$H$312</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$I$311:$I$312</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -2953,8 +2953,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3270,7 +3270,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR8.3 需要串口 (1=需要)</a:t>
+              <a:t>KR8.2 按名字找到板子</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3437,8 +3437,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
-          <min val="46306"/>
+          <max val="46309"/>
+          <min val="46307"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3480,7 +3480,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>是/否</a:t>
+                  <a:t>s</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -3512,7 +3512,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR9.1 转子遥测可用 (1=可用)</a:t>
+              <a:t>KR8.3 需要串口 (1=需要)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3679,8 +3679,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46309"/>
-          <min val="46307"/>
+          <max val="46308"/>
+          <min val="46306"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3754,7 +3754,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR9.2 远程升级失败自动回滚 (1=有)</a:t>
+              <a:t>KR9.1 转子遥测可用 (1=可用)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3996,7 +3996,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR10.1 可实时播放内容数</a:t>
+              <a:t>KR9.2 远程升级失败自动回滚 (1=有)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4053,49 +4053,6 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'指标趋势'!C378</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="triangle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="ED7D31"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="ED7D31"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <xVal>
-            <numRef>
-              <f>'指标趋势'!$A$379</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'指标趋势'!$C$379</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
               <f>'指标趋势'!E378</f>
             </strRef>
           </tx>
@@ -4128,8 +4085,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'指标趋势'!G378</f>
@@ -4164,8 +4121,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'指标趋势'!I378</f>
@@ -4249,7 +4206,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>个</a:t>
+                  <a:t>是/否</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -4281,7 +4238,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KR10.2 交互方式数</a:t>
+              <a:t>KR10.1 可实时播放内容数</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -4534,7 +4491,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>种</a:t>
+                  <a:t>个</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -4555,6 +4512,291 @@
 </file>
 
 <file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>KR10.2 交互方式数</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <scatterStyle val="lineMarker"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!B412</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="2E75B6"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$413</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$B$413</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!C412</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="triangle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="ED7D31"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$A$413</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$C$413</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!E412</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$D$413:$D$414</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$E$413:$E$414</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!G412</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$F$413:$F$414</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$G$413:$G$414</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'指标趋势'!I412</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'指标趋势'!$H$413:$H$414</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'指标趋势'!$I$413:$I$414</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="46309"/>
+          <min val="46307"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日期</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="mm-dd" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>种</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="span"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -4743,7 +4985,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -7367,6 +7609,28 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>410</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="25" name="Chart 25"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId25"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -8580,7 +8844,7 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6 (gw5a_bridge/p1 verify ALL PASS)</t>
+          <t>dr1v90 1995be8 (D15 阶段 1, 主会话复验)</t>
         </is>
       </c>
       <c r="Q15" s="8" t="n">
@@ -9008,9 +9272,17 @@
           <t>越小越好</t>
         </is>
       </c>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="6" t="inlineStr"/>
+      <c r="I22" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
       <c r="L22" s="3" t="n">
         <v>12</v>
       </c>
@@ -9020,13 +9292,19 @@
       <c r="N22" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O22" s="11" t="inlineStr">
-        <is>
-          <t>⏸</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr"/>
-      <c r="Q22" s="8" t="n"/>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/d13-boot fdbb217 (d13_boot/runs/levers, 串口真实复位时刻)</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="n">
+        <v>0.7594936708860759</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n"/>
@@ -9105,7 +9383,7 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>34</v>
+        <v>25.6</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>46308</v>
@@ -9131,11 +9409,11 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.78125</v>
       </c>
     </row>
     <row r="25">
@@ -9562,7 +9840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I397"/>
+  <dimension ref="A1:I414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11455,7 +11733,7 @@
     <row r="292">
       <c r="A292" s="17" t="inlineStr">
         <is>
-          <t>KR8.4 上电到转稳全亮 (s, 越小越好)</t>
+          <t>KR8.1 上电到 0° 片亮起 (停转) (s, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -11475,20 +11753,88 @@
           <t>仿真/台架</t>
         </is>
       </c>
+      <c r="D293" s="18" t="inlineStr">
+        <is>
+          <t>V0 目标 日期</t>
+        </is>
+      </c>
+      <c r="E293" s="18" t="inlineStr">
+        <is>
+          <t>V0 目标</t>
+        </is>
+      </c>
+      <c r="F293" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标 日期</t>
+        </is>
+      </c>
+      <c r="G293" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标</t>
+        </is>
+      </c>
+      <c r="H293" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标 日期</t>
+        </is>
+      </c>
+      <c r="I293" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B294" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="C294" s="3" t="n"/>
+      <c r="D294" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="B294" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="C294" s="3" t="n"/>
+      <c r="E294" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F294" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G294" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H294" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="I294" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="D295" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E295" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F295" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G295" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H295" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I295" s="3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="17" t="inlineStr">
         <is>
-          <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
+          <t>KR8.4 上电到转稳全亮 (s, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -11508,88 +11854,20 @@
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D310" s="18" t="inlineStr">
-        <is>
-          <t>V0 目标 日期</t>
-        </is>
-      </c>
-      <c r="E310" s="18" t="inlineStr">
-        <is>
-          <t>V0 目标</t>
-        </is>
-      </c>
-      <c r="F310" s="18" t="inlineStr">
-        <is>
-          <t>V1 目标 日期</t>
-        </is>
-      </c>
-      <c r="G310" s="18" t="inlineStr">
-        <is>
-          <t>V1 目标</t>
-        </is>
-      </c>
-      <c r="H310" s="18" t="inlineStr">
-        <is>
-          <t>V2 目标 日期</t>
-        </is>
-      </c>
-      <c r="I310" s="18" t="inlineStr">
-        <is>
-          <t>V2 目标</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B311" s="3" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C311" s="3" t="n"/>
-      <c r="D311" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="E311" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F311" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="G311" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H311" s="19" t="n">
-        <v>46307</v>
-      </c>
-      <c r="I311" s="3" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="D312" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="E312" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F312" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="G312" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H312" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I312" s="3" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="326">
       <c r="A326" s="17" t="inlineStr">
         <is>
-          <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
+          <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -11642,55 +11920,55 @@
     </row>
     <row r="328">
       <c r="A328" s="19" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B328" s="3" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="C328" s="3" t="n"/>
       <c r="D328" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E328" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F328" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H328" s="19" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I328" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="329">
       <c r="D329" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E329" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F329" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H329" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I329" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="17" t="inlineStr">
         <is>
-          <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
+          <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
         </is>
       </c>
     </row>
@@ -11743,55 +12021,55 @@
     </row>
     <row r="345">
       <c r="A345" s="19" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B345" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C345" s="3" t="n"/>
       <c r="D345" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="E345" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F345" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="G345" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H345" s="19" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="I345" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
       <c r="D346" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E346" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F346" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G346" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H346" s="19" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="I346" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="17" t="inlineStr">
         <is>
-          <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
+          <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -11892,7 +12170,7 @@
     <row r="377">
       <c r="A377" s="17" t="inlineStr">
         <is>
-          <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
+          <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -11948,28 +12226,26 @@
         <v>46308</v>
       </c>
       <c r="B379" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C379" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C379" s="3" t="n"/>
       <c r="D379" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E379" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F379" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="G379" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H379" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I379" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -11977,25 +12253,25 @@
         <v>46309</v>
       </c>
       <c r="E380" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F380" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="G380" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H380" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="I380" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="17" t="inlineStr">
         <is>
-          <t>KR10.2 交互方式数 (种, 越大越好)</t>
+          <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
         </is>
       </c>
     </row>
@@ -12051,28 +12327,28 @@
         <v>46308</v>
       </c>
       <c r="B396" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C396" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D396" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="E396" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F396" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="G396" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H396" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="I396" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="397">
@@ -12080,18 +12356,121 @@
         <v>46309</v>
       </c>
       <c r="E397" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F397" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="G397" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H397" s="19" t="n">
         <v>46309</v>
       </c>
       <c r="I397" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="17" t="inlineStr">
+        <is>
+          <t>KR10.2 交互方式数 (种, 越大越好)</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="18" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B412" s="18" t="inlineStr">
+        <is>
+          <t>实测</t>
+        </is>
+      </c>
+      <c r="C412" s="18" t="inlineStr">
+        <is>
+          <t>仿真/台架</t>
+        </is>
+      </c>
+      <c r="D412" s="18" t="inlineStr">
+        <is>
+          <t>V0 目标 日期</t>
+        </is>
+      </c>
+      <c r="E412" s="18" t="inlineStr">
+        <is>
+          <t>V0 目标</t>
+        </is>
+      </c>
+      <c r="F412" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标 日期</t>
+        </is>
+      </c>
+      <c r="G412" s="18" t="inlineStr">
+        <is>
+          <t>V1 目标</t>
+        </is>
+      </c>
+      <c r="H412" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标 日期</t>
+        </is>
+      </c>
+      <c r="I412" s="18" t="inlineStr">
+        <is>
+          <t>V2 目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B413" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C413" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D413" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E413" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F413" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G413" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H413" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="I413" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="D414" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E414" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F414" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G414" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H414" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I414" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12691,7 +13070,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>task/pls-2047 (fb89d07)</t>
+          <t>9ba9af0 离线 26/27 (测试用例过时), 待修复后上板</t>
         </is>
       </c>
     </row>
@@ -12727,7 +13106,7 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>task/ul-fmt-30hz (7164f44)</t>
+          <t>台架 240M 档 + 1.2G PRBS 位流已出 (6c3dfdb), 待交付复验</t>
         </is>
       </c>
     </row>
@@ -12877,7 +13256,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>task/rotor-ops (05c4231，返工中)</t>
+          <t>7ef55e1 离线 3 遍过; 上板 16/16 过一轮 (旧提交), V3 待补测</t>
         </is>
       </c>
     </row>
@@ -13057,7 +13436,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>task/d12-latency</t>
+          <t>764f81d; 晚间 WiFi 差两次上板未过, 待主机空闲复测</t>
         </is>
       </c>
     </row>
@@ -13093,7 +13472,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>task/d13-boot</t>
+          <t>9630437 已装板: 复位→亮起 15.8 s / 找板 25.6 s; 余 2 项待用户批准写启动文件 (fdbb217)</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13508,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>task/d14-content</t>
+          <t>离线复验过 + 用户实转看过 (ffbfeeb, geo 循环 956e1ff); 待正式上板验收</t>
         </is>
       </c>
     </row>
@@ -13165,7 +13544,7 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>task/d15-color</t>
+          <t>阶段 1 合主线 1995be8; 阶段 2 待 D2/D12/D13 合并</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15576,16 +15955,16 @@
         <v>46308</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>KR5.1</t>
+          <t>KR4.2</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
+          <t>链路色深 12-bit 已验证 (1=是)</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -15598,17 +15977,17 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>仿真</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 1995be8 (D15 阶段 1, 主会话复验)</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
+          <t>WiFi 端 32 bit 像素 (X2R10G10B10) 黄金/PL 仿真一致; 硬件未验</t>
         </is>
       </c>
     </row>
@@ -15621,12 +16000,12 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>KR5.1</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>左右镜像已核实 (1=已核)</t>
+          <t>几何 LUT 复现正确 (1=逐字节复现)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -15635,7 +16014,7 @@
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
@@ -15644,12 +16023,12 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>2047 是否整体左右镜像未核</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS</t>
         </is>
       </c>
     </row>
@@ -15676,7 +16055,7 @@
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -15685,12 +16064,12 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6 (VOXSLICE_M90.md 10-13 节)</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>用户实转核实: 旧表镜像, 已更正为 0decad54</t>
+          <t>2047 是否整体左右镜像未核</t>
         </is>
       </c>
     </row>
@@ -15699,39 +16078,39 @@
         <v>46308</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>KR7.1</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>丢帧/迟到率</t>
+          <t>左右镜像已核实 (1=已核)</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>是/否</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>台架</t>
+          <t>V0 2047</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f</t>
+          <t>dr1v90 49031f6 (VOXSLICE_M90.md 10-13 节)</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
+          <t>用户实转核实: 旧表镜像, 已更正为 0decad54</t>
         </is>
       </c>
     </row>
@@ -15758,7 +16137,7 @@
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
@@ -15767,12 +16146,12 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 473abcf</t>
+          <t>dr1v90 71d006f</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
+          <t>纯切片 30 Hz 硅上尾部 late 0.2%</t>
         </is>
       </c>
     </row>
@@ -15803,17 +16182,17 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>V0 2047</t>
+          <t>台架</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 473abcf</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>实时推流 624 s NAK 0 / forced 0</t>
+          <t>暂停 netguard 后 late/miss 0 (10 s 一阵 late 来自 netguard)</t>
         </is>
       </c>
     </row>
@@ -15826,21 +16205,21 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>KR7.2</t>
+          <t>KR7.1</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>连续无故障: 软件链路 (假转, 无人值守)</t>
+          <t>丢帧/迟到率</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
@@ -15854,7 +16233,7 @@
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>实时推流连续 624 s 无故障 (未做更长)</t>
+          <t>实时推流 624 s NAK 0 / forced 0</t>
         </is>
       </c>
     </row>
@@ -15863,25 +16242,25 @@
         <v>46308</v>
       </c>
       <c r="B62" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>KR8.2</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>按名字找到板子</t>
+          <t>连续无故障: 软件链路 (假转, 无人值守)</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>34</v>
+        <v>0.17</v>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
@@ -15890,12 +16269,12 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>实时推流连续 624 s 无故障 (未做更长)</t>
         </is>
       </c>
     </row>
@@ -15904,25 +16283,25 @@
         <v>46308</v>
       </c>
       <c r="B63" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>KR9.1</t>
+          <t>KR8.1</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>转子遥测可用 (1=可用)</t>
+          <t>上电到 0° 片亮起 (停转)</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>是/否</t>
+          <t>s</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
@@ -15931,12 +16310,12 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
+          <t>dr1v90 task/d13-boot fdbb217 (d13_boot/runs/levers, 串口真实复位时刻)</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+          <t>D13 两轮后: 复位→0° 片亮起 (原 38.7 s → 20.1 → 15.8)</t>
         </is>
       </c>
     </row>
@@ -15945,44 +16324,167 @@
         <v>46308</v>
       </c>
       <c r="B64" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>KR8.2</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>按名字找到板子</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 b0f6b5d</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>无串口自重启后 34 s 按名字找到并 ssh 上</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>KR8.2</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>按名字找到板子</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/d13-boot fdbb217</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>D13 后找板 (原 34 → 30 → 25.6 s); IP 已固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B66" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>KR9.1</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>转子遥测可用 (1=可用)</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>dr1v90 task/rotor-ops 05c4231</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>D7 返工中 (首次复验 T5 偶发 FAIL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="20" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>KR9.2</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>远程升级失败自动回滚 (1=有)</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>是/否</t>
         </is>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F67" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>V0 2047</t>
         </is>
       </c>
-      <c r="H64" s="6" t="inlineStr">
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>dr1v90 task/rotor-ops 05c4231</t>
         </is>
       </c>
-      <c r="I64" s="6" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>D7 返工中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I64"/>
+  <autoFilter ref="A1:I67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -353,7 +353,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>阶段达成率趋势 (V0 达成率 / V1 准备度)</a:t>
+              <a:t>阶段达成率趋势 (V0 / V1 / V2)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -444,6 +444,49 @@
           <val>
             <numRef>
               <f>'每日进展'!$I$4:$I$5</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'每日进展'!J3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="70AD47"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'每日进展'!$G$4:$G$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'每日进展'!$J$4:$J$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -8273,12 +8316,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>V1 准备度</t>
+          <t>V1 达成率</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>V2 距离</t>
+          <t>V2 达成率</t>
         </is>
       </c>
     </row>
@@ -8289,80 +8332,80 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>29/48</t>
+          <t>26/39</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>KR 18/25 + 交付 11/23  —  V0 达成率 = (V0 目标已达标的 KR 数 + 阶段为 V0 或 V1准备 的已完成交付数) ÷ (有 V0 目标的 KR 总数 + 阶段为 V0 或 V1准备 的交付总数)。V1 的准备算在 V0 里。KR 是否达标 = 最新硬件实测 vs V0 目标 (krs.csv 人工状态可覆盖)。</t>
+          <t>KR 18/25 + 交付 8/14 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>0.3333</v>
+        <v>0.4103</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>0</v>
+        <v>0.234</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.7444</v>
+        <v>0.1961</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>V1 准备度</t>
+          <t>V1 达成率</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4468085106382979</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>21/47</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>V1 准备度 = 阶段为 V1准备 的已完成交付数 ÷ 阶段为 V1准备 的交付总数 (阶段列见 deliverables.csv；没填阶段的交付不计)。</t>
+          <t>KR 10/24 + 交付 11/23 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.6042</v>
+        <v>0.6667</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0.3333</v>
+        <v>0.4468</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.6919</v>
+        <v>0.3922</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>V2 距离</t>
+          <t>V2 达成率</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.6919279458100754</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>15.91/23</t>
+          <t>20/51</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>23 个 KR 的达成度之和 / 个数  —  V2 距离 = 「距 V2 达成%」的平均值，只算有 V2 目标的数值型 KR (最新值相对 V2 目标的达成度，越大越接近终极目标)。</t>
+          <t>KR 9/24 + 交付 11/27 — KR 是否达到 P 目标 = 截至该日的最新硬件实测值 vs P 目标 (仿真/台架点不算达标)。</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -14188,7 +14231,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>5</v>
@@ -14202,7 +14245,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>7</v>
@@ -14216,7 +14259,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>8</v>
@@ -14228,7 +14271,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>10</v>
@@ -14240,7 +14283,7 @@
         <v>46311</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>15</v>
@@ -14252,7 +14295,7 @@
         <v>46312</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>19</v>
@@ -14264,7 +14307,7 @@
         <v>46313</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>19</v>
@@ -14276,7 +14319,7 @@
         <v>46314</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>19</v>
@@ -14288,7 +14331,7 @@
         <v>46315</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>20</v>
@@ -14300,7 +14343,7 @@
         <v>46316</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>20</v>
@@ -14312,7 +14355,7 @@
         <v>46317</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>22</v>
@@ -14324,7 +14367,7 @@
         <v>46318</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>22</v>
@@ -14336,7 +14379,7 @@
         <v>46319</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>23</v>
@@ -15239,6 +15282,142 @@
       <c r="H47" s="7" t="inlineStr">
         <is>
           <t>task/d16-ddr</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>V2-1</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>T2 自研 SoC 板 (32 bit DDR + PL 读带宽)</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>7;4</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
+      <c r="G48" s="25" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>V2-2</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>2 期上行 1.2G 实测</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>2;3</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+      <c r="G49" s="25" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>V2-3</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>2 期 192×216 面板映射</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="17" t="n"/>
+      <c r="G50" s="25" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>V2-4</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>2 期 30 Hz 整机上转子</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>2期</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
+      <c r="G51" s="25" t="inlineStr">
+        <is>
+          <t>⏸</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-13.xlsx
+++ b/docs/progress/显性目的进度_2026-10-13.xlsx
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -237,13 +237,19 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8261,7 +8267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8332,16 +8338,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>26/39</t>
+          <t>26/36</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>KR 18/25 + 交付 8/14 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
+          <t>KR 18/25 + 交付 8/11 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
@@ -8364,29 +8370,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.4468085106382979</v>
+        <v>0.4772727272727273</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>21/47</t>
+          <t>21/44</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>KR 10/24 + 交付 11/23 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 10/24 + 交付 11/20 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.6667</v>
+        <v>0.7222</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0.4468</v>
+        <v>0.4773</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.3922</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
@@ -8396,16 +8402,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.392156862745098</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>20/51</t>
+          <t>20/48</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KR 9/24 + 交付 11/27 — KR 是否达到 P 目标 = 截至该日的最新硬件实测值 vs P 目标 (仿真/台架点不算达标)。</t>
+          <t>KR 9/24 + 交付 11/24 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
     </row>
@@ -8851,816 +8857,1711 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>每日流水 (daily_log.csv，按天倒序)</t>
+          <t>阶段出口清单 — V0 出口  (已打勾 3/8；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>条目</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>关联项进度</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>①2047 PL 切片上板通过</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>D2 (0/1)</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>②主机实时推流 15 fps</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>D1 (1/1)</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>③几何更正 + 镜像已核实</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2 (1/1)</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>④复位到亮起 ≤12 s、找板 ≤20 s</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>KR8.1;KR8.2;D13 (0/3)</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>⑤无串口远程运维：遥测 + 升级失败自动回滚</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>D7;KR9.1;KR9.2 (0/3)</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>⑥软件链路无人值守 ≥8 h</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>KR7.2 (0/1)</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>⑦WiFi 端 12-bit 通路在 2047 上跑通</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>D15 (0/1)</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>⑧内容 ≥2 + 一种交互</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>KR10.1;KR10.2 (2/2)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>阶段出口清单 — V1 回板当天就绪  (已打勾 3/11；状态由关联项在当日是否完成/达标推出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>条目</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>关联项进度</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>①主控 1 期整合位流 (PL 切片 + 12-bit 上行，V3 引脚)</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>D10 (0/1)</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>②桥 1 期 6 链 24 Hz 位流</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>D5 (1/1)</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>③桥接收 + 1.2G PRBS 测试件</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>D4 (1/1)</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>④1 期几何 LUT + 校准工具</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>D6 (1/1)</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>⑤主控↔桥↔2260 联合仿真 0 错</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>D8 (0/1)</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>⑥全链路系统仿真</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>D9 (0/1)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>⑦C1 台架逐像素 0 错</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>D11 (0/1)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>⑧整机回板点亮步骤 + 一键脚本</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>人工状态</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>⑨硬件确认清单闭环：灯板 SDO→SDI 0Ω、CN3/CN6 n→n、R176–R181 等</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>人工状态</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>⑩面板映射 4 项信息到位</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>人工状态</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>⑪无串口运维可用</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>D7 (0/1)</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>风险表 (risks.csv；红 = 开，黄 = 监控，绿 = 关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>影响 / 应对</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>负责 · 登记日期 · 来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>1.2G 可能过不了</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>影响：DR1 无 SERDES，09-22 DR1↔DR1 1.2G 全死
+应对：退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>主会话+硬件 · 2026-10-13 · 10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>1 期 4,296 片/s 桥链路余量仅 0.40%</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>影响：时钟偏差会丢帧
+应对：退路降到 22 Hz（用户定保持 24 Hz）</t>
+        </is>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>影响：每块下半屏黑
+应对：硬件确认并补 0Ω</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>2260 从未收到合法 ACK（疑物理通路）</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>影响：1 期显示可能起不来
+应对：验证板一颗一组针对此问题，回板验证</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>硬件+主会话 · 2026-10-13 · 10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>2 期 DDR 带宽：16 bit 余量约 11%，32 bit 像素超限</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>影响：2 期 32 bit 像素带宽不够
+应对：B 线 T2 板 32 bit DDR + PL 读口 ≥200 MHz/分端口</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>偶发慢读 133 µs &gt; 30 Hz 片窗 110 µs</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>影响：偶发迟到掉片
+应对：D16 预取缓冲 + 降争用</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>WiFi/主机负载造成延迟尾巴（10-13 晚 p99 334 ms）</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>影响：延迟抖动超标
+应对：演示时停重任务；后续增量帧</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>影响：高速下接触不良/脱落
+应对：T2 板留 eMMC、打胶</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>D 盘 EIO（IP-guard 驱动）</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>影响：构建/提交偶发失败
+应对：看门狗自动重挂 + 构建放 WSL 本地盘</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>1 期面板映射缺 4 项信息</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>影响：1 期桥表无法定稿
+应对：问硬件同事</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>每日流水 (daily_log.csv，按天倒序)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="17" t="n">
+    <row r="66">
+      <c r="A66" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>E6</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="17" t="n">
+    <row r="67">
+      <c r="A67" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>E7</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="17" t="n">
+    <row r="68">
+      <c r="A68" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="17" t="n">
+    <row r="69">
+      <c r="A69" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B69" s="19" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="17" t="n">
+    <row r="70">
+      <c r="A70" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B70" s="16" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="17" t="n">
+    <row r="71">
+      <c r="A71" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B71" s="17" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="17" t="n">
+    <row r="72">
+      <c r="A72" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="17" t="n">
+    <row r="73">
+      <c r="A73" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B73" s="16" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="n">
+    <row r="74">
+      <c r="A74" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="n">
+    <row r="75">
+      <c r="A75" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B75" s="19" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="17" t="n">
+    <row r="76">
+      <c r="A76" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="17" t="n">
+    <row r="77">
+      <c r="A77" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B77" s="17" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="17" t="n">
+    <row r="78">
+      <c r="A78" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B78" s="16" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>D14</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="17" t="n">
+    <row r="79">
+      <c r="A79" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B79" s="16" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="17" t="n">
+    <row r="80">
+      <c r="A80" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B42" s="19" t="inlineStr">
+      <c r="B80" s="17" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="17" t="n">
+    <row r="81">
+      <c r="A81" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B81" s="19" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="17" t="n">
+    <row r="82">
+      <c r="A82" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B44" s="19" t="inlineStr">
+      <c r="B82" s="17" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="17" t="n">
+    <row r="83">
+      <c r="A83" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="17" t="n">
+    <row r="84">
+      <c r="A84" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B46" s="18" t="inlineStr">
+      <c r="B84" s="19" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="n">
+    <row r="85">
+      <c r="A85" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>D15</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="17" t="n">
+    <row r="86">
+      <c r="A86" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B86" s="22" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>D3;D4;D5</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="17" t="n">
+    <row r="87">
+      <c r="A87" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B49" s="20" t="inlineStr">
+      <c r="B87" s="22" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr"/>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr"/>
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="17" t="n">
+    <row r="88">
+      <c r="A88" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B88" s="14" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr"/>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr"/>
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="17" t="n">
+    <row r="89">
+      <c r="A89" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B51" s="20" t="inlineStr">
+      <c r="B89" s="22" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr"/>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr"/>
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="17" t="n">
+    <row r="90">
+      <c r="A90" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B52" s="20" t="inlineStr">
+      <c r="B90" s="22" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="17" t="n">
+    <row r="91">
+      <c r="A91" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B91" s="22" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>D11</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="17" t="n">
+    <row r="92">
+      <c r="A92" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B54" s="20" t="inlineStr">
+      <c r="B92" s="22" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>D12;D13;D14</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="17" t="n">
+    <row r="93">
+      <c r="A93" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B93" s="22" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="n">
+    <row r="94">
+      <c r="A94" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B56" s="20" t="inlineStr">
+      <c r="B94" s="22" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>D15;D16</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="17" t="n">
+    <row r="95">
+      <c r="A95" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B57" s="20" t="inlineStr">
+      <c r="B95" s="22" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>KR5.2</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="17" t="n">
+    <row r="96">
+      <c r="A96" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B58" s="18" t="inlineStr">
+      <c r="B96" s="19" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="17" t="n">
+    <row r="97">
+      <c r="A97" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr"/>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr"/>
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -9701,7 +10602,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>POV3D 显性目的进度看板 — 2026-10-13  (当前期 V0；状态按「最新硬件实测 vs 当前期目标」自动判定，krs.csv 人工状态列可覆盖)</t>
         </is>
@@ -9836,7 +10737,7 @@
       <c r="I4" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -9863,15 +10764,15 @@
           <t>dr1v90 596b191 / 9bf16ad</t>
         </is>
       </c>
-      <c r="Q4" s="22" t="n">
+      <c r="Q4" s="24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="n"/>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
+      <c r="A5" s="25" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>KR1.2</t>
@@ -9895,7 +10796,7 @@
       <c r="I5" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="J5" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -9922,15 +10823,15 @@
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
-      <c r="Q5" s="22" t="n">
+      <c r="Q5" s="24" t="n">
         <v>0.7368421052631579</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="n"/>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
+      <c r="A6" s="25" t="n"/>
+      <c r="B6" s="25" t="n"/>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="25" t="n"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>KR1.7</t>
@@ -9954,7 +10855,7 @@
       <c r="I6" s="6" t="n">
         <v>236.6</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -9981,15 +10882,15 @@
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="n">
+      <c r="Q6" s="24" t="n">
         <v>0.5071851225697379</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="n"/>
-      <c r="B7" s="23" t="n"/>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
+      <c r="A7" s="25" t="n"/>
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="25" t="n"/>
+      <c r="D7" s="25" t="n"/>
       <c r="E7" s="7" t="inlineStr">
         <is>
           <t>KR1.3</t>
@@ -10013,7 +10914,7 @@
       <c r="I7" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -10040,15 +10941,15 @@
           <t>claude_memory/project_m90_wifi_p2p_1012.md</t>
         </is>
       </c>
-      <c r="Q7" s="22" t="n">
+      <c r="Q7" s="24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="n"/>
-      <c r="B8" s="23" t="n"/>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="23" t="n"/>
+      <c r="A8" s="25" t="n"/>
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="25" t="n"/>
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>KR1.4</t>
@@ -10072,7 +10973,7 @@
       <c r="I8" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -10099,15 +11000,15 @@
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
-      <c r="Q8" s="22" t="n">
+      <c r="Q8" s="24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="n"/>
-      <c r="B9" s="23" t="n"/>
-      <c r="C9" s="23" t="n"/>
-      <c r="D9" s="23" t="n"/>
+      <c r="A9" s="25" t="n"/>
+      <c r="B9" s="25" t="n"/>
+      <c r="C9" s="25" t="n"/>
+      <c r="D9" s="25" t="n"/>
       <c r="E9" s="7" t="inlineStr">
         <is>
           <t>KR1.5</t>
@@ -10131,7 +11032,7 @@
       <c r="I9" s="6" t="n">
         <v>17.3</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -10154,13 +11055,13 @@
           <t>dr1v90 596b191</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="n"/>
+      <c r="Q9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="n"/>
-      <c r="B10" s="24" t="n"/>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="24" t="n"/>
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>KR1.6</t>
@@ -10184,7 +11085,7 @@
       <c r="I10" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -10211,7 +11112,7 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md (D9 首次转起来 640–654 RPM)</t>
         </is>
       </c>
-      <c r="Q10" s="22" t="n">
+      <c r="Q10" s="24" t="n">
         <v>0.7200000000000001</v>
       </c>
     </row>
@@ -10257,7 +11158,7 @@
       <c r="I11" s="6" t="n">
         <v>21.7</v>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -10284,7 +11185,7 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q11" s="22" t="n">
+      <c r="Q11" s="24" t="n">
         <v>0.7233333333333333</v>
       </c>
     </row>
@@ -10330,7 +11231,7 @@
       <c r="I12" s="6" t="n">
         <v>28800</v>
       </c>
-      <c r="J12" s="17" t="n">
+      <c r="J12" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -10357,15 +11258,15 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="n">
+      <c r="Q12" s="24" t="n">
         <v>0.6944444444444444</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="n"/>
-      <c r="B13" s="24" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
+      <c r="A13" s="26" t="n"/>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>KR3.2</t>
@@ -10389,7 +11290,7 @@
       <c r="I13" s="6" t="n">
         <v>142</v>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -10416,7 +11317,7 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q13" s="22" t="n">
+      <c r="Q13" s="24" t="n">
         <v>0.2347107438016529</v>
       </c>
     </row>
@@ -10434,7 +11335,7 @@
           <t>显示优化</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>⏸ 无数据 / 未开始</t>
         </is>
@@ -10462,7 +11363,7 @@
       <c r="I14" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -10489,15 +11390,15 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q14" s="22" t="n">
+      <c r="Q14" s="24" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="n"/>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="24" t="n"/>
+      <c r="A15" s="26" t="n"/>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
       <c r="E15" s="7" t="inlineStr">
         <is>
           <t>KR4.2</t>
@@ -10521,7 +11422,7 @@
       <c r="I15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="17" t="n">
+      <c r="J15" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -10538,7 +11439,7 @@
       <c r="N15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="25" t="inlineStr">
+      <c r="O15" s="27" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -10548,7 +11449,7 @@
           <t>dr1v90 1995be8 (D15 阶段 1, 主会话复验)</t>
         </is>
       </c>
-      <c r="Q15" s="22" t="n">
+      <c r="Q15" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10594,7 +11495,7 @@
       <c r="I16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="17" t="n">
+      <c r="J16" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -10621,15 +11522,15 @@
           <t>dr1v90 44ed2cd</t>
         </is>
       </c>
-      <c r="Q16" s="22" t="n">
+      <c r="Q16" s="24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n"/>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="24" t="n"/>
+      <c r="A17" s="26" t="n"/>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
       <c r="E17" s="7" t="inlineStr">
         <is>
           <t>KR5.2</t>
@@ -10653,7 +11554,7 @@
       <c r="I17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -10680,7 +11581,7 @@
           <t>dr1v90 49031f6 (VOXSLICE_M90.md 10-13 节)</t>
         </is>
       </c>
-      <c r="Q17" s="22" t="n">
+      <c r="Q17" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10726,7 +11627,7 @@
       <c r="I18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -10753,7 +11654,7 @@
           <t>dr1v90 3bc5736</t>
         </is>
       </c>
-      <c r="Q18" s="22" t="n">
+      <c r="Q18" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10771,7 +11672,7 @@
           <t>稳定</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -10799,7 +11700,7 @@
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="J19" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -10826,15 +11727,15 @@
           <t>dr1v90 596b191</t>
         </is>
       </c>
-      <c r="Q19" s="22" t="n">
+      <c r="Q19" s="24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="n"/>
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n"/>
+      <c r="A20" s="25" t="n"/>
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
           <t>KR7.2</t>
@@ -10858,7 +11759,7 @@
       <c r="I20" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -10875,7 +11776,7 @@
       <c r="N20" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="O20" s="18" t="inlineStr">
+      <c r="O20" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -10885,15 +11786,15 @@
           <t>dr1v90 596b191</t>
         </is>
       </c>
-      <c r="Q20" s="22" t="n">
+      <c r="Q20" s="24" t="n">
         <v>0.007083333333333334</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="n"/>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="24" t="n"/>
+      <c r="A21" s="26" t="n"/>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>KR7.3</t>
@@ -10915,7 +11816,7 @@
         </is>
       </c>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="17" t="n"/>
+      <c r="J21" s="21" t="n"/>
       <c r="K21" s="7" t="inlineStr"/>
       <c r="L21" s="6" t="n">
         <v>1</v>
@@ -10926,13 +11827,13 @@
       <c r="N21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O21" s="25" t="inlineStr">
+      <c r="O21" s="27" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr"/>
-      <c r="Q21" s="22" t="n"/>
+      <c r="Q21" s="24" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -10948,7 +11849,7 @@
           <t>运维</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -10976,7 +11877,7 @@
       <c r="I22" s="6" t="n">
         <v>15.8</v>
       </c>
-      <c r="J22" s="17" t="n">
+      <c r="J22" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -10993,7 +11894,7 @@
       <c r="N22" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="O22" s="18" t="inlineStr">
+      <c r="O22" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11003,15 +11904,15 @@
           <t>dr1v90 task/d13-boot fdbb217 (d13_boot/runs/levers, 串口真实复位时刻)</t>
         </is>
       </c>
-      <c r="Q22" s="22" t="n">
+      <c r="Q22" s="24" t="n">
         <v>0.7594936708860759</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="n"/>
-      <c r="B23" s="23" t="n"/>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="23" t="n"/>
+      <c r="A23" s="25" t="n"/>
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="25" t="n"/>
       <c r="E23" s="7" t="inlineStr">
         <is>
           <t>KR8.4</t>
@@ -11035,7 +11936,7 @@
       <c r="I23" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="J23" s="17" t="n">
+      <c r="J23" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -11046,7 +11947,7 @@
       <c r="L23" s="6" t="n"/>
       <c r="M23" s="6" t="n"/>
       <c r="N23" s="6" t="n"/>
-      <c r="O23" s="18" t="inlineStr">
+      <c r="O23" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11056,13 +11957,13 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q23" s="22" t="n"/>
+      <c r="Q23" s="24" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="n"/>
-      <c r="B24" s="23" t="n"/>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="23" t="n"/>
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
       <c r="E24" s="7" t="inlineStr">
         <is>
           <t>KR8.2</t>
@@ -11086,7 +11987,7 @@
       <c r="I24" s="6" t="n">
         <v>25.6</v>
       </c>
-      <c r="J24" s="17" t="n">
+      <c r="J24" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -11103,7 +12004,7 @@
       <c r="N24" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="O24" s="18" t="inlineStr">
+      <c r="O24" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11113,15 +12014,15 @@
           <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
-      <c r="Q24" s="22" t="n">
+      <c r="Q24" s="24" t="n">
         <v>0.78125</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="n"/>
-      <c r="B25" s="24" t="n"/>
-      <c r="C25" s="24" t="n"/>
-      <c r="D25" s="24" t="n"/>
+      <c r="A25" s="26" t="n"/>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>KR8.3</t>
@@ -11145,7 +12046,7 @@
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="17" t="n">
+      <c r="J25" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -11172,7 +12073,7 @@
           <t>dr1v90 30d82f9</t>
         </is>
       </c>
-      <c r="Q25" s="22" t="n">
+      <c r="Q25" s="24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11190,7 +12091,7 @@
           <t>运维</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -11218,7 +12119,7 @@
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="17" t="n">
+      <c r="J26" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -11235,7 +12136,7 @@
       <c r="N26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O26" s="18" t="inlineStr">
+      <c r="O26" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11245,15 +12146,15 @@
           <t>dr1v90 task/rotor-ops 05c4231</t>
         </is>
       </c>
-      <c r="Q26" s="22" t="n">
+      <c r="Q26" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="n"/>
-      <c r="B27" s="24" t="n"/>
-      <c r="C27" s="24" t="n"/>
-      <c r="D27" s="24" t="n"/>
+      <c r="A27" s="26" t="n"/>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>KR9.2</t>
@@ -11277,7 +12178,7 @@
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="17" t="n">
+      <c r="J27" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -11294,7 +12195,7 @@
       <c r="N27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O27" s="18" t="inlineStr">
+      <c r="O27" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11304,7 +12205,7 @@
           <t>dr1v90 task/rotor-ops 05c4231</t>
         </is>
       </c>
-      <c r="Q27" s="22" t="n">
+      <c r="Q27" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11350,7 +12251,7 @@
       <c r="I28" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="J28" s="17" t="n">
+      <c r="J28" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -11377,15 +12278,15 @@
           <t>dr1v90 task/d14-content ffbfeeb + 用户实转观看</t>
         </is>
       </c>
-      <c r="Q28" s="22" t="n">
+      <c r="Q28" s="24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="n"/>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
+      <c r="A29" s="26" t="n"/>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
           <t>KR10.2</t>
@@ -11409,7 +12310,7 @@
       <c r="I29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="17" t="n">
+      <c r="J29" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
@@ -11436,12 +12337,12 @@
           <t>dr1v90 live_push/README.md</t>
         </is>
       </c>
-      <c r="Q29" s="22" t="n">
+      <c r="Q29" s="24" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
@@ -11453,43 +12354,43 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="B32" s="27" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>达成当前期目标</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>进行中 / 未达标</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
       </c>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B34" s="29" t="inlineStr">
         <is>
           <t>无数据 / 未开始</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="B35" s="27" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>退步 / 阻塞</t>
         </is>
@@ -11561,54 +12462,54 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>KR1.1 内容刷新率 (假转, 管线能力) (fps, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H4" s="29" t="inlineStr">
+      <c r="H4" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I4" s="29" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -11714,54 +12615,54 @@
       <c r="C11" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>KR1.2 端到端延迟 p50 (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="D21" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F21" s="29" t="inlineStr">
+      <c r="F21" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G21" s="29" t="inlineStr">
+      <c r="G21" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H21" s="29" t="inlineStr">
+      <c r="H21" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I21" s="29" t="inlineStr">
+      <c r="I21" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -11815,54 +12716,54 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="28" t="inlineStr">
+      <c r="A37" s="30" t="inlineStr">
         <is>
           <t>KR1.7 端到端延迟抖动 p99 (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C38" s="29" t="inlineStr">
+      <c r="C38" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D38" s="29" t="inlineStr">
+      <c r="D38" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E38" s="29" t="inlineStr">
+      <c r="E38" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F38" s="29" t="inlineStr">
+      <c r="F38" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G38" s="29" t="inlineStr">
+      <c r="G38" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H38" s="29" t="inlineStr">
+      <c r="H38" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I38" s="29" t="inlineStr">
+      <c r="I38" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -11916,54 +12817,54 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="28" t="inlineStr">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t>KR1.3 WiFi 可用带宽 (Mbit/s, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B55" s="29" t="inlineStr">
+      <c r="B55" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C55" s="29" t="inlineStr">
+      <c r="C55" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D55" s="29" t="inlineStr">
+      <c r="D55" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E55" s="29" t="inlineStr">
+      <c r="E55" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F55" s="29" t="inlineStr">
+      <c r="F55" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G55" s="29" t="inlineStr">
+      <c r="G55" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H55" s="29" t="inlineStr">
+      <c r="H55" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I55" s="29" t="inlineStr">
+      <c r="I55" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12051,54 +12952,54 @@
       <c r="C60" s="6" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="28" t="inlineStr">
+      <c r="A71" s="30" t="inlineStr">
         <is>
           <t>KR1.4 主机出帧耗时 p99 (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29" t="inlineStr">
+      <c r="A72" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B72" s="29" t="inlineStr">
+      <c r="B72" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C72" s="29" t="inlineStr">
+      <c r="C72" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D72" s="29" t="inlineStr">
+      <c r="D72" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E72" s="29" t="inlineStr">
+      <c r="E72" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F72" s="29" t="inlineStr">
+      <c r="F72" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G72" s="29" t="inlineStr">
+      <c r="G72" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H72" s="29" t="inlineStr">
+      <c r="H72" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I72" s="29" t="inlineStr">
+      <c r="I72" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12159,34 +13060,34 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="28" t="inlineStr">
+      <c r="A88" s="30" t="inlineStr">
         <is>
           <t>KR1.5 板上切片耗时 (每帧) (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29" t="inlineStr">
+      <c r="A89" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B89" s="29" t="inlineStr">
+      <c r="B89" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C89" s="29" t="inlineStr">
+      <c r="C89" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D89" s="29" t="inlineStr">
+      <c r="D89" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E89" s="29" t="inlineStr">
+      <c r="E89" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
@@ -12223,54 +13124,54 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="28" t="inlineStr">
+      <c r="A105" s="30" t="inlineStr">
         <is>
           <t>KR1.6 内容刷新率 (实转上屏) (fps, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="29" t="inlineStr">
+      <c r="A106" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B106" s="29" t="inlineStr">
+      <c r="B106" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C106" s="29" t="inlineStr">
+      <c r="C106" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D106" s="29" t="inlineStr">
+      <c r="D106" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E106" s="29" t="inlineStr">
+      <c r="E106" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F106" s="29" t="inlineStr">
+      <c r="F106" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G106" s="29" t="inlineStr">
+      <c r="G106" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H106" s="29" t="inlineStr">
+      <c r="H106" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I106" s="29" t="inlineStr">
+      <c r="I106" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12324,54 +13225,54 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="28" t="inlineStr">
+      <c r="A122" s="30" t="inlineStr">
         <is>
           <t>KR2.1 体帧率 (Hz, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="29" t="inlineStr">
+      <c r="A123" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B123" s="29" t="inlineStr">
+      <c r="B123" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C123" s="29" t="inlineStr">
+      <c r="C123" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D123" s="29" t="inlineStr">
+      <c r="D123" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E123" s="29" t="inlineStr">
+      <c r="E123" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F123" s="29" t="inlineStr">
+      <c r="F123" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G123" s="29" t="inlineStr">
+      <c r="G123" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H123" s="29" t="inlineStr">
+      <c r="H123" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I123" s="29" t="inlineStr">
+      <c r="I123" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12441,54 +13342,54 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="28" t="inlineStr">
+      <c r="A139" s="30" t="inlineStr">
         <is>
           <t>KR3.1 每面像素数 (px, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="29" t="inlineStr">
+      <c r="A140" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B140" s="29" t="inlineStr">
+      <c r="B140" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C140" s="29" t="inlineStr">
+      <c r="C140" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D140" s="29" t="inlineStr">
+      <c r="D140" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E140" s="29" t="inlineStr">
+      <c r="E140" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F140" s="29" t="inlineStr">
+      <c r="F140" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G140" s="29" t="inlineStr">
+      <c r="G140" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H140" s="29" t="inlineStr">
+      <c r="H140" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I140" s="29" t="inlineStr">
+      <c r="I140" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12549,54 +13450,54 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="28" t="inlineStr">
+      <c r="A156" s="30" t="inlineStr">
         <is>
           <t>KR3.2 每圈片数 (片, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="29" t="inlineStr">
+      <c r="A157" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B157" s="29" t="inlineStr">
+      <c r="B157" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C157" s="29" t="inlineStr">
+      <c r="C157" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D157" s="29" t="inlineStr">
+      <c r="D157" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E157" s="29" t="inlineStr">
+      <c r="E157" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F157" s="29" t="inlineStr">
+      <c r="F157" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G157" s="29" t="inlineStr">
+      <c r="G157" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H157" s="29" t="inlineStr">
+      <c r="H157" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I157" s="29" t="inlineStr">
+      <c r="I157" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12675,54 +13576,54 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="28" t="inlineStr">
+      <c r="A173" s="30" t="inlineStr">
         <is>
           <t>KR4.1 色深 (bit/通道, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="29" t="inlineStr">
+      <c r="A174" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B174" s="29" t="inlineStr">
+      <c r="B174" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C174" s="29" t="inlineStr">
+      <c r="C174" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D174" s="29" t="inlineStr">
+      <c r="D174" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E174" s="29" t="inlineStr">
+      <c r="E174" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F174" s="29" t="inlineStr">
+      <c r="F174" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G174" s="29" t="inlineStr">
+      <c r="G174" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H174" s="29" t="inlineStr">
+      <c r="H174" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I174" s="29" t="inlineStr">
+      <c r="I174" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12810,54 +13711,54 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="28" t="inlineStr">
+      <c r="A190" s="30" t="inlineStr">
         <is>
           <t>KR4.2 链路色深 12-bit 已验证 (1=是) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="29" t="inlineStr">
+      <c r="A191" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B191" s="29" t="inlineStr">
+      <c r="B191" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C191" s="29" t="inlineStr">
+      <c r="C191" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D191" s="29" t="inlineStr">
+      <c r="D191" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E191" s="29" t="inlineStr">
+      <c r="E191" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F191" s="29" t="inlineStr">
+      <c r="F191" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G191" s="29" t="inlineStr">
+      <c r="G191" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H191" s="29" t="inlineStr">
+      <c r="H191" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I191" s="29" t="inlineStr">
+      <c r="I191" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12911,54 +13812,54 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="28" t="inlineStr">
+      <c r="A207" s="30" t="inlineStr">
         <is>
           <t>KR5.1 几何 LUT 复现正确 (1=逐字节复现) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="29" t="inlineStr">
+      <c r="A208" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B208" s="29" t="inlineStr">
+      <c r="B208" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C208" s="29" t="inlineStr">
+      <c r="C208" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D208" s="29" t="inlineStr">
+      <c r="D208" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E208" s="29" t="inlineStr">
+      <c r="E208" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F208" s="29" t="inlineStr">
+      <c r="F208" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G208" s="29" t="inlineStr">
+      <c r="G208" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H208" s="29" t="inlineStr">
+      <c r="H208" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I208" s="29" t="inlineStr">
+      <c r="I208" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13019,54 +13920,54 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="28" t="inlineStr">
+      <c r="A224" s="30" t="inlineStr">
         <is>
           <t>KR5.2 左右镜像已核实 (1=已核) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="29" t="inlineStr">
+      <c r="A225" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B225" s="29" t="inlineStr">
+      <c r="B225" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C225" s="29" t="inlineStr">
+      <c r="C225" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D225" s="29" t="inlineStr">
+      <c r="D225" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E225" s="29" t="inlineStr">
+      <c r="E225" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F225" s="29" t="inlineStr">
+      <c r="F225" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G225" s="29" t="inlineStr">
+      <c r="G225" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H225" s="29" t="inlineStr">
+      <c r="H225" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I225" s="29" t="inlineStr">
+      <c r="I225" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13120,54 +14021,54 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="28" t="inlineStr">
+      <c r="A241" s="30" t="inlineStr">
         <is>
           <t>KR6.1 停转自动低亮 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="29" t="inlineStr">
+      <c r="A242" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B242" s="29" t="inlineStr">
+      <c r="B242" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C242" s="29" t="inlineStr">
+      <c r="C242" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D242" s="29" t="inlineStr">
+      <c r="D242" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E242" s="29" t="inlineStr">
+      <c r="E242" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F242" s="29" t="inlineStr">
+      <c r="F242" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G242" s="29" t="inlineStr">
+      <c r="G242" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H242" s="29" t="inlineStr">
+      <c r="H242" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I242" s="29" t="inlineStr">
+      <c r="I242" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13221,54 +14122,54 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="28" t="inlineStr">
+      <c r="A258" s="30" t="inlineStr">
         <is>
           <t>KR7.1 丢帧/迟到率 (%, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="29" t="inlineStr">
+      <c r="A259" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B259" s="29" t="inlineStr">
+      <c r="B259" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C259" s="29" t="inlineStr">
+      <c r="C259" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D259" s="29" t="inlineStr">
+      <c r="D259" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E259" s="29" t="inlineStr">
+      <c r="E259" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F259" s="29" t="inlineStr">
+      <c r="F259" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G259" s="29" t="inlineStr">
+      <c r="G259" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H259" s="29" t="inlineStr">
+      <c r="H259" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I259" s="29" t="inlineStr">
+      <c r="I259" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13324,54 +14225,54 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="28" t="inlineStr">
+      <c r="A275" s="30" t="inlineStr">
         <is>
           <t>KR7.2 连续无故障: 软件链路 (假转, 无人值守) (h, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="29" t="inlineStr">
+      <c r="A276" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B276" s="29" t="inlineStr">
+      <c r="B276" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C276" s="29" t="inlineStr">
+      <c r="C276" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D276" s="29" t="inlineStr">
+      <c r="D276" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E276" s="29" t="inlineStr">
+      <c r="E276" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F276" s="29" t="inlineStr">
+      <c r="F276" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G276" s="29" t="inlineStr">
+      <c r="G276" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H276" s="29" t="inlineStr">
+      <c r="H276" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I276" s="29" t="inlineStr">
+      <c r="I276" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13432,54 +14333,54 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="28" t="inlineStr">
+      <c r="A292" s="30" t="inlineStr">
         <is>
           <t>KR8.1 上电到 0° 片亮起 (停转) (s, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="29" t="inlineStr">
+      <c r="A293" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B293" s="29" t="inlineStr">
+      <c r="B293" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C293" s="29" t="inlineStr">
+      <c r="C293" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D293" s="29" t="inlineStr">
+      <c r="D293" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E293" s="29" t="inlineStr">
+      <c r="E293" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F293" s="29" t="inlineStr">
+      <c r="F293" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G293" s="29" t="inlineStr">
+      <c r="G293" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H293" s="29" t="inlineStr">
+      <c r="H293" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I293" s="29" t="inlineStr">
+      <c r="I293" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13533,24 +14434,24 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="28" t="inlineStr">
+      <c r="A309" s="30" t="inlineStr">
         <is>
           <t>KR8.4 上电到转稳全亮 (s, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="29" t="inlineStr">
+      <c r="A310" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B310" s="29" t="inlineStr">
+      <c r="B310" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C310" s="29" t="inlineStr">
+      <c r="C310" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
@@ -13566,54 +14467,54 @@
       <c r="C311" s="6" t="n"/>
     </row>
     <row r="326">
-      <c r="A326" s="28" t="inlineStr">
+      <c r="A326" s="30" t="inlineStr">
         <is>
           <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="29" t="inlineStr">
+      <c r="A327" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B327" s="29" t="inlineStr">
+      <c r="B327" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C327" s="29" t="inlineStr">
+      <c r="C327" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D327" s="29" t="inlineStr">
+      <c r="D327" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E327" s="29" t="inlineStr">
+      <c r="E327" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F327" s="29" t="inlineStr">
+      <c r="F327" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G327" s="29" t="inlineStr">
+      <c r="G327" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H327" s="29" t="inlineStr">
+      <c r="H327" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I327" s="29" t="inlineStr">
+      <c r="I327" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13667,54 +14568,54 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="28" t="inlineStr">
+      <c r="A343" s="30" t="inlineStr">
         <is>
           <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="29" t="inlineStr">
+      <c r="A344" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B344" s="29" t="inlineStr">
+      <c r="B344" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C344" s="29" t="inlineStr">
+      <c r="C344" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D344" s="29" t="inlineStr">
+      <c r="D344" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E344" s="29" t="inlineStr">
+      <c r="E344" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F344" s="29" t="inlineStr">
+      <c r="F344" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G344" s="29" t="inlineStr">
+      <c r="G344" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H344" s="29" t="inlineStr">
+      <c r="H344" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I344" s="29" t="inlineStr">
+      <c r="I344" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13768,54 +14669,54 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="28" t="inlineStr">
+      <c r="A360" s="30" t="inlineStr">
         <is>
           <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="29" t="inlineStr">
+      <c r="A361" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B361" s="29" t="inlineStr">
+      <c r="B361" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C361" s="29" t="inlineStr">
+      <c r="C361" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D361" s="29" t="inlineStr">
+      <c r="D361" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E361" s="29" t="inlineStr">
+      <c r="E361" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F361" s="29" t="inlineStr">
+      <c r="F361" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G361" s="29" t="inlineStr">
+      <c r="G361" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H361" s="29" t="inlineStr">
+      <c r="H361" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I361" s="29" t="inlineStr">
+      <c r="I361" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13869,54 +14770,54 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="28" t="inlineStr">
+      <c r="A377" s="30" t="inlineStr">
         <is>
           <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="29" t="inlineStr">
+      <c r="A378" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B378" s="29" t="inlineStr">
+      <c r="B378" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C378" s="29" t="inlineStr">
+      <c r="C378" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D378" s="29" t="inlineStr">
+      <c r="D378" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E378" s="29" t="inlineStr">
+      <c r="E378" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F378" s="29" t="inlineStr">
+      <c r="F378" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G378" s="29" t="inlineStr">
+      <c r="G378" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H378" s="29" t="inlineStr">
+      <c r="H378" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I378" s="29" t="inlineStr">
+      <c r="I378" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13970,54 +14871,54 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="28" t="inlineStr">
+      <c r="A394" s="30" t="inlineStr">
         <is>
           <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="29" t="inlineStr">
+      <c r="A395" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B395" s="29" t="inlineStr">
+      <c r="B395" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C395" s="29" t="inlineStr">
+      <c r="C395" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D395" s="29" t="inlineStr">
+      <c r="D395" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E395" s="29" t="inlineStr">
+      <c r="E395" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F395" s="29" t="inlineStr">
+      <c r="F395" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G395" s="29" t="inlineStr">
+      <c r="G395" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H395" s="29" t="inlineStr">
+      <c r="H395" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I395" s="29" t="inlineStr">
+      <c r="I395" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14073,54 +14974,54 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="28" t="inlineStr">
+      <c r="A411" s="30" t="inlineStr">
         <is>
           <t>KR10.2 交互方式数 (种, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="29" t="inlineStr">
+      <c r="A412" s="31" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B412" s="29" t="inlineStr">
+      <c r="B412" s="31" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C412" s="29" t="inlineStr">
+      <c r="C412" s="31" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D412" s="29" t="inlineStr">
+      <c r="D412" s="31" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E412" s="29" t="inlineStr">
+      <c r="E412" s="31" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F412" s="29" t="inlineStr">
+      <c r="F412" s="31" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G412" s="29" t="inlineStr">
+      <c r="G412" s="31" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H412" s="29" t="inlineStr">
+      <c r="H412" s="31" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I412" s="29" t="inlineStr">
+      <c r="I412" s="31" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14456,10 +15357,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E25" s="17" t="n">
+      <c r="E25" s="21" t="n">
         <v>46307</v>
       </c>
-      <c r="F25" s="17" t="n">
+      <c r="F25" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
@@ -14494,10 +15395,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E26" s="21" t="n">
         <v>46307</v>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="G26" s="16" t="inlineStr">
@@ -14532,10 +15433,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E27" s="21" t="n">
         <v>46307</v>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F27" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="G27" s="16" t="inlineStr">
@@ -14570,10 +15471,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E28" s="17" t="n">
+      <c r="E28" s="21" t="n">
         <v>46307</v>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="G28" s="16" t="inlineStr">
@@ -14608,10 +15509,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E29" s="17" t="n">
+      <c r="E29" s="21" t="n">
         <v>46307</v>
       </c>
-      <c r="F29" s="17" t="n">
+      <c r="F29" s="21" t="n">
         <v>46307</v>
       </c>
       <c r="G29" s="16" t="inlineStr">
@@ -14646,10 +15547,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="F30" s="17" t="n">
+      <c r="F30" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="G30" s="16" t="inlineStr">
@@ -14684,10 +15585,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E31" s="17" t="n">
+      <c r="E31" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="G31" s="16" t="inlineStr">
@@ -14722,10 +15623,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E32" s="17" t="n">
+      <c r="E32" s="21" t="n">
         <v>46309</v>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="G32" s="16" t="inlineStr">
@@ -14760,11 +15661,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E33" s="17" t="n">
+      <c r="E33" s="21" t="n">
         <v>46311</v>
       </c>
-      <c r="F33" s="17" t="n"/>
-      <c r="G33" s="18" t="inlineStr">
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -14796,11 +15697,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E34" s="21" t="n">
         <v>46311</v>
       </c>
-      <c r="F34" s="17" t="n"/>
-      <c r="G34" s="18" t="inlineStr">
+      <c r="F34" s="21" t="n"/>
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -14832,10 +15733,10 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E35" s="17" t="n">
+      <c r="E35" s="21" t="n">
         <v>46311</v>
       </c>
-      <c r="F35" s="17" t="n">
+      <c r="F35" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="G35" s="16" t="inlineStr">
@@ -14870,10 +15771,10 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E36" s="21" t="n">
         <v>46312</v>
       </c>
-      <c r="F36" s="17" t="n">
+      <c r="F36" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="G36" s="16" t="inlineStr">
@@ -14908,10 +15809,10 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E37" s="17" t="n">
+      <c r="E37" s="21" t="n">
         <v>46310</v>
       </c>
-      <c r="F37" s="17" t="n">
+      <c r="F37" s="21" t="n">
         <v>46308</v>
       </c>
       <c r="G37" s="16" t="inlineStr">
@@ -14946,11 +15847,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E38" s="17" t="n">
+      <c r="E38" s="21" t="n">
         <v>46312</v>
       </c>
-      <c r="F38" s="17" t="n"/>
-      <c r="G38" s="18" t="inlineStr">
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -14982,11 +15883,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E39" s="17" t="n">
+      <c r="E39" s="21" t="n">
         <v>46315</v>
       </c>
-      <c r="F39" s="17" t="n"/>
-      <c r="G39" s="25" t="inlineStr">
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="27" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15018,11 +15919,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E40" s="17" t="n">
+      <c r="E40" s="21" t="n">
         <v>46317</v>
       </c>
-      <c r="F40" s="17" t="n"/>
-      <c r="G40" s="25" t="inlineStr">
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="27" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15054,11 +15955,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E41" s="17" t="n">
+      <c r="E41" s="21" t="n">
         <v>46317</v>
       </c>
-      <c r="F41" s="17" t="n"/>
-      <c r="G41" s="25" t="inlineStr">
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="27" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15090,11 +15991,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E42" s="17" t="n">
+      <c r="E42" s="21" t="n">
         <v>46319</v>
       </c>
-      <c r="F42" s="17" t="n"/>
-      <c r="G42" s="25" t="inlineStr">
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="27" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15126,11 +16027,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E43" s="17" t="n">
+      <c r="E43" s="21" t="n">
         <v>46310</v>
       </c>
-      <c r="F43" s="17" t="n"/>
-      <c r="G43" s="18" t="inlineStr">
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -15162,11 +16063,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E44" s="17" t="n">
+      <c r="E44" s="21" t="n">
         <v>46311</v>
       </c>
-      <c r="F44" s="17" t="n"/>
-      <c r="G44" s="18" t="inlineStr">
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -15198,11 +16099,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E45" s="17" t="n">
+      <c r="E45" s="21" t="n">
         <v>46311</v>
       </c>
-      <c r="F45" s="17" t="n"/>
-      <c r="G45" s="18" t="inlineStr">
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -15234,11 +16135,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E46" s="17" t="n">
+      <c r="E46" s="21" t="n">
         <v>46312</v>
       </c>
-      <c r="F46" s="17" t="n"/>
-      <c r="G46" s="18" t="inlineStr">
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -15270,11 +16171,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E47" s="17" t="n">
+      <c r="E47" s="21" t="n">
         <v>46312</v>
       </c>
-      <c r="F47" s="17" t="n"/>
-      <c r="G47" s="18" t="inlineStr">
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="19" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -15306,9 +16207,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E48" s="17" t="n"/>
-      <c r="F48" s="17" t="n"/>
-      <c r="G48" s="25" t="inlineStr">
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="27" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15340,9 +16241,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E49" s="17" t="n"/>
-      <c r="F49" s="17" t="n"/>
-      <c r="G49" s="25" t="inlineStr">
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="27" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15374,9 +16275,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E50" s="17" t="n"/>
-      <c r="F50" s="17" t="n"/>
-      <c r="G50" s="25" t="inlineStr">
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="27" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15408,9 +16309,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E51" s="17" t="n"/>
-      <c r="F51" s="17" t="n"/>
-      <c r="G51" s="25" t="inlineStr">
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="27" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15496,48 +16397,48 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="21" t="n">
         <v>46308</v>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="21" t="n">
         <v>46312</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="21" t="n">
         <v>46317</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="21" t="n">
         <v>46319</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="21" t="n">
         <v>46336</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="21" t="n">
         <v>46338</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="21" t="n">
         <v>46343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>对角线 (y = x)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="32" t="n">
         <v>46308</v>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="32" t="n">
         <v>46308</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="32" t="n">
         <v>46343</v>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="32" t="n">
         <v>46343</v>
       </c>
     </row>
@@ -15615,7 +16516,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="n">
+      <c r="A2" s="32" t="n">
         <v>46157</v>
       </c>
       <c r="B2" s="7" t="n">
@@ -15656,7 +16557,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="n">
+      <c r="A3" s="32" t="n">
         <v>46157</v>
       </c>
       <c r="B3" s="7" t="n">
@@ -15697,7 +16598,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="n">
+      <c r="A4" s="32" t="n">
         <v>46231</v>
       </c>
       <c r="B4" s="7" t="n">
@@ -15738,7 +16639,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="n">
+      <c r="A5" s="32" t="n">
         <v>46231</v>
       </c>
       <c r="B5" s="7" t="n">
@@ -15779,7 +16680,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n">
+      <c r="A6" s="32" t="n">
         <v>46231</v>
       </c>
       <c r="B6" s="7" t="n">
@@ -15820,7 +16721,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="32" t="n">
         <v>46238</v>
       </c>
       <c r="B7" s="7" t="n">
@@ -15861,7 +16762,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="32" t="n">
         <v>46238</v>
       </c>
       <c r="B8" s="7" t="n">
@@ -15902,7 +16803,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="32" t="n">
         <v>46238</v>
       </c>
       <c r="B9" s="7" t="n">
@@ -15943,7 +16844,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="A10" s="32" t="n">
         <v>46239</v>
       </c>
       <c r="B10" s="7" t="n">
@@ -15984,7 +16885,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="32" t="n">
         <v>46240</v>
       </c>
       <c r="B11" s="7" t="n">
@@ -16025,7 +16926,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="A12" s="32" t="n">
         <v>46254</v>
       </c>
       <c r="B12" s="7" t="n">
@@ -16066,7 +16967,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="32" t="n">
         <v>46259</v>
       </c>
       <c r="B13" s="7" t="n">
@@ -16107,7 +17008,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="A14" s="32" t="n">
         <v>46260</v>
       </c>
       <c r="B14" s="7" t="n">
@@ -16148,7 +17049,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="A15" s="32" t="n">
         <v>46267</v>
       </c>
       <c r="B15" s="7" t="n">
@@ -16189,7 +17090,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="A16" s="32" t="n">
         <v>46279</v>
       </c>
       <c r="B16" s="7" t="n">
@@ -16230,7 +17131,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="32" t="n">
         <v>46280</v>
       </c>
       <c r="B17" s="7" t="n">
@@ -16271,7 +17172,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="A18" s="32" t="n">
         <v>46280</v>
       </c>
       <c r="B18" s="7" t="n">
@@ -16312,7 +17213,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B19" s="7" t="n">
@@ -16353,7 +17254,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="n">
+      <c r="A20" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B20" s="7" t="n">
@@ -16394,7 +17295,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B21" s="7" t="n">
@@ -16435,7 +17336,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="n">
+      <c r="A22" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B22" s="7" t="n">
@@ -16476,7 +17377,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="n">
+      <c r="A23" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B23" s="7" t="n">
@@ -16517,7 +17418,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="n">
+      <c r="A24" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B24" s="7" t="n">
@@ -16558,7 +17459,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="n">
+      <c r="A25" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B25" s="7" t="n">
@@ -16599,7 +17500,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="n">
+      <c r="A26" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B26" s="7" t="n">
@@ -16640,7 +17541,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="n">
+      <c r="A27" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B27" s="7" t="n">
@@ -16681,7 +17582,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="n">
+      <c r="A28" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B28" s="7" t="n">
@@ -16722,7 +17623,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="n">
+      <c r="A29" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B29" s="7" t="n">
@@ -16763,7 +17664,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="n">
+      <c r="A30" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B30" s="7" t="n">
@@ -16804,7 +17705,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="n">
+      <c r="A31" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B31" s="7" t="n">
@@ -16845,7 +17746,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="n">
+      <c r="A32" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B32" s="7" t="n">
@@ -16886,7 +17787,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="n">
+      <c r="A33" s="32" t="n">
         <v>46307</v>
       </c>
       <c r="B33" s="7" t="n">
@@ -16927,7 +17828,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="n">
+      <c r="A34" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B34" s="7" t="n">
@@ -16968,7 +17869,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="n">
+      <c r="A35" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B35" s="7" t="n">
@@ -17009,7 +17910,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="n">
+      <c r="A36" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B36" s="7" t="n">
@@ -17050,7 +17951,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="n">
+      <c r="A37" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B37" s="7" t="n">
@@ -17091,7 +17992,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="30" t="n">
+      <c r="A38" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B38" s="7" t="n">
@@ -17132,7 +18033,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="n">
+      <c r="A39" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B39" s="7" t="n">
@@ -17173,7 +18074,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="n">
+      <c r="A40" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B40" s="7" t="n">
@@ -17214,7 +18115,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="n">
+      <c r="A41" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B41" s="7" t="n">
@@ -17255,7 +18156,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="n">
+      <c r="A42" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B42" s="7" t="n">
@@ -17296,7 +18197,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="n">
+      <c r="A43" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B43" s="7" t="n">
@@ -17337,7 +18238,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="n">
+      <c r="A44" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B44" s="7" t="n">
@@ -17378,7 +18279,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="n">
+      <c r="A45" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B45" s="7" t="n">
@@ -17419,7 +18320,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="n">
+      <c r="A46" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B46" s="7" t="n">
@@ -17460,7 +18361,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30" t="n">
+      <c r="A47" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B47" s="7" t="n">
@@ -17501,7 +18402,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30" t="n">
+      <c r="A48" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B48" s="7" t="n">
@@ -17542,7 +18443,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="n">
+      <c r="A49" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B49" s="7" t="n">
@@ -17583,7 +18484,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="n">
+      <c r="A50" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B50" s="7" t="n">
@@ -17624,7 +18525,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="n">
+      <c r="A51" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B51" s="7" t="n">
@@ -17665,7 +18566,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30" t="n">
+      <c r="A52" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B52" s="7" t="n">
@@ -17706,7 +18607,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30" t="n">
+      <c r="A53" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B53" s="7" t="n">
@@ -17747,7 +18648,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30" t="n">
+      <c r="A54" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B54" s="7" t="n">
@@ -17788,7 +18689,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="n">
+      <c r="A55" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B55" s="7" t="n">
@@ -17829,7 +18730,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30" t="n">
+      <c r="A56" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B56" s="7" t="n">
@@ -17870,7 +18771,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30" t="n">
+      <c r="A57" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B57" s="7" t="n">
@@ -17911,7 +18812,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30" t="n">
+      <c r="A58" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B58" s="7" t="n">
@@ -17952,7 +18853,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30" t="n">
+      <c r="A59" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B59" s="7" t="n">
@@ -17993,7 +18894,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30" t="n">
+      <c r="A60" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B60" s="7" t="n">
@@ -18034,7 +18935,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="n">
+      <c r="A61" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B61" s="7" t="n">
@@ -18075,7 +18976,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="n">
+      <c r="A62" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B62" s="7" t="n">
@@ -18116,7 +19017,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30" t="n">
+      <c r="A63" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B63" s="7" t="n">
@@ -18157,7 +19058,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="n">
+      <c r="A64" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B64" s="7" t="n">
@@ -18198,7 +19099,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="n">
+      <c r="A65" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B65" s="7" t="n">
@@ -18239,7 +19140,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30" t="n">
+      <c r="A66" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B66" s="7" t="n">
@@ -18280,7 +19181,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="n">
+      <c r="A67" s="32" t="n">
         <v>46308</v>
       </c>
       <c r="B67" s="7" t="n">
